--- a/tools/precos/planilhas/precos-oficiais-medicube.xlsx
+++ b/tools/precos/planilhas/precos-oficiais-medicube.xlsx
@@ -41,12 +41,17 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F4E8"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -72,7 +77,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -81,6 +86,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -582,7 +588,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -641,7 +647,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -678,12 +684,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MB003323</t>
+          <t>MB003292</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Affordable Glass Glow 7-Day Set: rotina de 5 passos com exossomos e colágeno</t>
+          <t>Azelaic Acid 16 Calming Serum: sérum calmante com ácido azelaico e niacinamida</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -692,28 +698,24 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>561.9</v>
+        <v>174.9</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Affordable Glass Glow 7-Day Skincare Set</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Collagen Jelly Cream</t>
-        </is>
-      </c>
+          <t>Azelaic Acid 16 Calming Serum</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" s="4" t="n">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>155</v>
+        <v>26</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -722,7 +724,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/affordable-glass-glow-7-day-skincare-set?variant=41592205738032</t>
+          <t>https://medicube.us/products/azelaic-acid-16-calming-serum</t>
         </is>
       </c>
       <c r="L4" s="2">
@@ -737,12 +739,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MB003292</t>
+          <t>MB003229</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Azelaic Acid 16 Calming Serum: sérum calmante com ácido azelaico e niacinamida</t>
+          <t>Azelaic Acid Capsule Foam Cleanser: espuma com cápsulas de ácido azelaico</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -751,24 +753,24 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>174.9</v>
+        <v>145.9</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Azelaic Acid 16 Calming Serum</t>
+          <t>Azelaic Acid Capsule Foam Cleanser</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -777,7 +779,7 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/azelaic-acid-16-calming-serum</t>
+          <t>https://medicube.us/products/azelaic-acid-capsule-foam-cleanser</t>
         </is>
       </c>
       <c r="L5" s="2">
@@ -792,12 +794,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MB003229</t>
+          <t>MB003225</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Azelaic Acid Capsule Foam Cleanser: espuma com cápsulas de ácido azelaico</t>
+          <t>Azelaic Acid Exosome Shot: sérum com microespículas, ácido azelaico e exossomos</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,24 +808,28 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>145.9</v>
+        <v>160.9</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Azelaic Acid Capsule Foam Cleanser</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>Azelaic Acid Exosome Shot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MILD(2000)</t>
+        </is>
+      </c>
       <c r="H6" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -832,7 +838,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/azelaic-acid-capsule-foam-cleanser</t>
+          <t>https://medicube.us/products/azelaic-acid-exosome-shot?variant=43053899448368</t>
         </is>
       </c>
       <c r="L6" s="2">
@@ -847,12 +853,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MB003225</t>
+          <t>MB003226</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Azelaic Acid Exosome Shot: sérum com microespículas, ácido azelaico e exossomos</t>
+          <t>Azelaic Acid Niacinamide Clarifying Toner: tônico com 4% de ácido azelaico</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -861,29 +867,23 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>160.9</v>
+        <v>153.9</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Azelaic Acid Exosome Shot</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MILD(2000)</t>
-        </is>
-      </c>
+          <t>Azelaic Acid Niacinamide Clarifying Toner</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>24</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I7" s="4" t="n"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -891,7 +891,7 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/azelaic-acid-exosome-shot?variant=43053899448368</t>
+          <t>https://medicube.us/products/azelaic-acid-niacinamide-clarifying-toner</t>
         </is>
       </c>
       <c r="L7" s="2">
@@ -906,12 +906,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MB003226</t>
+          <t>MB003303</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Azelaic Acid Niacinamide Clarifying Toner: tônico com 4% de ácido azelaico</t>
+          <t>Collagen Glow Booster Milk Serum: sérum leitoso com colágeno e niacinamida 110 ml</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -920,23 +920,29 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>153.9</v>
+        <v>174.9</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Azelaic Acid Niacinamide Clarifying Toner</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Collagen Glow Booster Milk Serum</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
       <c r="H8" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="I8" s="4" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>26</v>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -944,7 +950,7 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/azelaic-acid-niacinamide-clarifying-toner</t>
+          <t>https://medicube.us/products/collagen-glow-booster-milk-serum?variant=41350297649200</t>
         </is>
       </c>
       <c r="L8" s="2">
@@ -959,12 +965,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MB003303</t>
+          <t>MB003305</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Collagen Glow Booster Milk Serum: sérum leitoso com colágeno e niacinamida 110 ml</t>
+          <t>Collagen Milky Glow Daytime Wrapping Mask: máscara peel-off de colágeno e leite</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -977,17 +983,21 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[Subscr.] Collagen Glow Booster Milk Serum</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Collagen Milky Glow Daytime Wrapping Mask</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
       <c r="H9" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I9" s="4" t="n"/>
       <c r="J9" t="inlineStr">
@@ -997,7 +1007,7 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/subscr-collagen-glow-booster-milk-serum</t>
+          <t>https://medicube.us/products/collagen-milk-toning-wrapping-mask?variant=42501172199472</t>
         </is>
       </c>
       <c r="L9" s="2">
@@ -1012,12 +1022,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MB003304</t>
+          <t>MB003317</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Collagen Glow Bubble Serum: sérum em mousse com 11 tipos de colágeno 100 ml</t>
+          <t>Collagen Niacinamide Jelly Cream: gel-creme de colágeno e niacinamida</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1026,24 +1036,28 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>174.9</v>
+        <v>104.9</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[US ONLY] Collagen Glow Bubble Serum</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>Collagen Niacinamide Jelly Cream</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>110ml</t>
+        </is>
+      </c>
       <c r="H10" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1052,7 +1066,7 @@
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/collagen-glow-bubble-serum</t>
+          <t>https://medicube.us/products/collagen-niacinamide-jelly-cream?variant=40889653493808</t>
         </is>
       </c>
       <c r="L10" s="2">
@@ -1067,12 +1081,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MB003305</t>
+          <t>MB003319</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Collagen Milky Glow Daytime Wrapping Mask: máscara peel-off de colágeno e leite</t>
+          <t>Collagen Swirl Duo: gel-creme de colágeno + creme de colágeno para misturar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1081,23 +1095,25 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>174.9</v>
+        <v>567.9</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[Subscr.] Collagen Milky Glow Daytime Wrapping Mask</t>
+          <t>Collagen Swirl Duo</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I11" s="4" t="n"/>
+        <v>49</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>78</v>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1105,7 +1121,7 @@
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/subscr-collagen-milky-glow-daytime-wrapping-mask</t>
+          <t>https://medicube.us/products/collagen-swirl-duo</t>
         </is>
       </c>
       <c r="L11" s="2">
@@ -1120,12 +1136,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MB003317</t>
+          <t>MB003278</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Collagen Niacinamide Jelly Cream: gel-creme de colágeno e niacinamida</t>
+          <t>Deep Peptide Radiance Mask: máscara em folha com 4 peptídeos e ácido hialurônico</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1134,28 +1150,28 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>104.9</v>
+        <v>42.9</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Collagen Niacinamide Jelly Cream</t>
+          <t>Deep Peptide Radiance Mask</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>110ml</t>
+          <t>2 MASKS</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1164,7 +1180,7 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/collagen-niacinamide-jelly-cream?variant=40889653493808</t>
+          <t>https://medicube.us/products/medicube-deep-peptide-radiance-mask-2ea?variant=40999586234416</t>
         </is>
       </c>
       <c r="L12" s="2">
@@ -1179,12 +1195,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MB003319</t>
+          <t>MB003280</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Collagen Swirl Duo: gel-creme de colágeno + creme de colágeno para misturar</t>
+          <t>Deep Reviving Bakuchiol Retinol Serum: sérum de retinol e bakuchiol 30 ml</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1193,24 +1209,28 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>567.9</v>
+        <v>174.9</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Collagen Swirl Duo</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Deep Reviving Bakuchiol Retinol Serum</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
       <c r="H13" s="4" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1219,7 +1239,7 @@
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/collagen-swirl-duo</t>
+          <t>https://medicube.us/products/deep-reviving-bakuchiol-retinol-serum?variant=41189259542576</t>
         </is>
       </c>
       <c r="L13" s="2">
@@ -1234,12 +1254,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MB003245</t>
+          <t>MB003250</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Conjunto AGE-R Spotless Radiance</t>
+          <t>Deep Reviving Peptide Eye Cream: creme para a área dos olhos com peptídeos 30 ml</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1248,37 +1268,33 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2179.9</v>
+        <v>188.9</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AGE-R Spotless Radiance Set</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Pink</t>
-        </is>
-      </c>
+          <t>Deep Reviving Peptide Eye Cream</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" s="4" t="n">
-        <v>299</v>
+        <v>26</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>529</v>
+        <v>28</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/age-r-spotless-radiance-set?variant=41769865838640</t>
+          <t>https://medicube.us/products/deep-reviving-peptide-eye-cream-1</t>
         </is>
       </c>
       <c r="L14" s="2">
@@ -1293,12 +1309,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MB003255</t>
+          <t>MB003244</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deep Glow Set: tônico, sérum e creme de colágeno em 3 passos</t>
+          <t>Deep Vita C Daily Quick Masks: 30 máscaras de 1 minuto com vitaminas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1307,24 +1323,24 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>509.9</v>
+        <v>254.9</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Deep Glow Set</t>
+          <t>Deep Vita C Daily Quick Masks</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" s="4" t="n">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>109</v>
+        <v>35</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1333,7 +1349,7 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/deep-glow-set-1</t>
+          <t>https://medicube.us/products/deep-vita-c-daily-quick-masks</t>
         </is>
       </c>
       <c r="L15" s="2">
@@ -1348,12 +1364,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MB003278</t>
+          <t>MB003281</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deep Peptide Radiance Mask: máscara em folha com 4 peptídeos e ácido hialurônico</t>
+          <t>Deep Vita C Pads: discos de vitamina C para tom uniforme (70 discos)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1362,28 +1378,28 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>42.9</v>
+        <v>169.9</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Deep Peptide Radiance Mask</t>
+          <t>Deep Vita C Pads</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2 MASKS</t>
+          <t>SINGLE</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1392,7 +1408,7 @@
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/medicube-deep-peptide-radiance-mask-2ea?variant=40999586234416</t>
+          <t>https://medicube.us/products/deep-vita-c-pad?variant=40708793172016</t>
         </is>
       </c>
       <c r="L16" s="2">
@@ -1407,12 +1423,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MB003280</t>
+          <t>MB003237</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Deep Reviving Bakuchiol Retinol Serum: sérum de retinol e bakuchiol 30 ml</t>
+          <t>Deep Vitamin C Capsule Serum: sérum de vitamina C em cápsulas com niacinamida</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1425,19 +1441,21 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[Subscr.] Deep Reviving Bakuchiol Retinol Serum</t>
+          <t>Deep Vitamin C Capsule Serum</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="I17" s="4" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>26</v>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1445,7 +1463,7 @@
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/subscr-deep-reviving-bakuchiol-retinol-serum</t>
+          <t>https://medicube.us/products/deep-vitamin-c-capsule-serum</t>
         </is>
       </c>
       <c r="L17" s="2">
@@ -1460,12 +1478,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MB003250</t>
+          <t>MB003257</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Deep Reviving Peptide Eye Cream: creme para a área dos olhos com peptídeos 30 ml</t>
+          <t>Glass Glow Duo: tônico e sérum com três tipos de colágeno</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1474,24 +1492,24 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>188.9</v>
+        <v>480.9</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deep Reviving Peptide Eye Cream</t>
+          <t>Glass Glow Duo</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" s="4" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1500,7 +1518,7 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/deep-reviving-peptide-eye-cream-1</t>
+          <t>https://medicube.us/products/triple-collagen-set</t>
         </is>
       </c>
       <c r="L18" s="2">
@@ -1515,12 +1533,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MB003282</t>
+          <t>MB003318</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Deep Vita C Capsule Cream: creme em cápsulas de vitamina C e niacinamida 55 g</t>
+          <t>Glazed Milk Duo: sérum leitoso de colágeno + máscara noturna peel-off</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1529,23 +1547,25 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>169.9</v>
+        <v>328.9</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[Subscr.] Deep Vita C Capsule Cream</t>
+          <t>Glazed Milk Duo</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="I19" s="4" t="n"/>
+        <v>45</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>52</v>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1553,7 +1573,7 @@
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/subscr-deep-vita-c-capsule-cream</t>
+          <t>https://medicube.us/products/glazed-milk-duo</t>
         </is>
       </c>
       <c r="L19" s="2">
@@ -1568,12 +1588,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MB003244</t>
+          <t>MB003300</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deep Vita C Daily Quick Masks: 30 máscaras de 1 minuto com vitaminas</t>
+          <t>Hyaluronic Acid Capsule Cream: creme com cápsulas de ácido hialurônico 55 g</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1582,24 +1602,28 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>254.9</v>
+        <v>169.9</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Deep Vita C Daily Quick Masks</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>Hyaluronic Acid Capsule Cream</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
       <c r="H20" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1608,7 +1632,7 @@
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/deep-vita-c-daily-quick-masks</t>
+          <t>https://medicube.us/products/hyaluronic-acid-capsule-cream?variant=42525945167920</t>
         </is>
       </c>
       <c r="L20" s="2">
@@ -1623,12 +1647,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MB003281</t>
+          <t>MB003268</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deep Vita C Pads: discos de vitamina C para tom uniforme (70 discos)</t>
+          <t>Hyaluronic Ceramide Moisturizing Jelly Cream: gel-creme com ácido hialurônico</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1637,21 +1661,21 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>169.9</v>
+        <v>189.9</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[Subscr.] Deep Vita C Pads</t>
+          <t>Hyaluronic Ceramide Moisturizing Jelly Cream</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" s="4" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="I21" s="4" t="n"/>
       <c r="J21" t="inlineStr">
@@ -1661,7 +1685,7 @@
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/subscr-deep-vita-c-pads</t>
+          <t>https://medicube.us/products/hyaluronic-ceramide-moisturizing-jelly-cream</t>
         </is>
       </c>
       <c r="L21" s="2">
@@ -1676,12 +1700,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MB003237</t>
+          <t>MB003267</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deep Vitamin C Capsule Serum: sérum de vitamina C em cápsulas com niacinamida</t>
+          <t>Hyaluronic Multi Peptide PDRN Serum: sérum bifásico com ácido hialurônico e PDRN</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1690,16 +1714,16 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>174.9</v>
+        <v>145.9</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Deep Vitamin C Capsule Serum</t>
+          <t>Hyaluronic Multi Peptide PDRN Serum</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1716,7 +1740,7 @@
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/deep-vitamin-c-capsule-serum</t>
+          <t>https://medicube.us/products/hyaluronic-multi-peptide-pdrn-serum</t>
         </is>
       </c>
       <c r="L22" s="2">
@@ -1731,12 +1755,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MB003257</t>
+          <t>MB003228</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Glass Glow Duo: tônico e sérum com três tipos de colágeno</t>
+          <t>Hypochlorous Acid Peel Mask: máscara em folha peel-off para cravos e poros</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1745,24 +1769,24 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>480.9</v>
+        <v>189.9</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Glass Glow Duo</t>
+          <t>Hypochlorous Acid Peel Mask</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" s="4" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1771,7 +1795,7 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/triple-collagen-set</t>
+          <t>https://medicube.us/products/hypochlorous-acid-peel-mask</t>
         </is>
       </c>
       <c r="L23" s="2">
@@ -1786,12 +1810,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MB003318</t>
+          <t>MB003331</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Glazed Milk Duo: sérum leitoso de colágeno + máscara noturna peel-off</t>
+          <t>Hypochlorous Acid Power Soothing Spray: spray calmante com ácido hipocloroso</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1800,24 +1824,24 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>328.9</v>
+        <v>159.9</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Glazed Milk Duo</t>
+          <t>Hypochlorous Acid Power Soothing Spray</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" s="4" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1826,7 +1850,7 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/glazed-milk-duo</t>
+          <t>https://medicube.us/products/hypochlorous-acid-power-soothing-spray</t>
         </is>
       </c>
       <c r="L24" s="2">
@@ -1841,12 +1865,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MB003300</t>
+          <t>MB003241</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hyaluronic Acid Capsule Cream: creme com cápsulas de ácido hialurônico 55 g</t>
+          <t>Hypochlorous Acid Rice Body Peel Shot: esfoliante corporal com ácido hipocloroso</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1855,21 +1879,21 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>169.9</v>
+        <v>204.9</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[Subscr.] Hyaluronic Acid Capsule Cream</t>
+          <t>Hypochlorous Acid Rice Body Peel Shot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" s="4" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I25" s="4" t="n"/>
       <c r="J25" t="inlineStr">
@@ -1879,7 +1903,7 @@
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/subscr-hyaluronic-acid-capsule-cream</t>
+          <t>https://medicube.us/products/hypochlorous-acid-rice-body-peel-shot</t>
         </is>
       </c>
       <c r="L25" s="2">
@@ -1894,12 +1918,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MB003268</t>
+          <t>MB003235</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hyaluronic Ceramide Moisturizing Jelly Cream: gel-creme com ácido hialurônico</t>
+          <t>Kojic Acid Turmeric Body Peel Shot: esfoliante corporal com ácido kójico e cúrcuma</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1908,21 +1932,21 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>189.9</v>
+        <v>203.9</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hyaluronic Ceramide Moisturizing Jelly Cream</t>
+          <t>Kojic Acid Turmeric Body Peel Shot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" s="4" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="I26" s="4" t="n"/>
       <c r="J26" t="inlineStr">
@@ -1932,7 +1956,7 @@
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/hyaluronic-ceramide-moisturizing-jelly-cream</t>
+          <t>https://medicube.us/products/kojic-acid-turmeric-body-peel-shot</t>
         </is>
       </c>
       <c r="L26" s="2">
@@ -1947,12 +1971,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MB003267</t>
+          <t>MB003243</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hyaluronic Multi Peptide PDRN Serum: sérum bifásico com ácido hialurônico e PDRN</t>
+          <t>Kojic Acid Turmeric Brightening Body Wash: sabonete líquido corporal iluminador</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1961,25 +1985,29 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>145.9</v>
+        <v>160.9</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hyaluronic Multi Peptide PDRN Serum</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>Kojic Acid Turmeric Brightening Body Wash</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>400ml</t>
+        </is>
+      </c>
       <c r="H27" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I27" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="I27" s="4" t="n">
-        <v>26</v>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1987,7 +2015,7 @@
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/hyaluronic-multi-peptide-pdrn-serum</t>
+          <t>https://medicube.us/products/kojic-acid-turmeric-brightening-body-wash?variant=43582251532336</t>
         </is>
       </c>
       <c r="L27" s="2">
@@ -2002,12 +2030,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MB003228</t>
+          <t>MB003298</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hypochlorous Acid Peel Mask: máscara em folha peel-off para cravos e poros</t>
+          <t>Kojic Acid Turmeric Capsule Serum: sérum em cápsulas com ácido kójico e cúrcuma</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2020,21 +2048,21 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hypochlorous Acid Peel Mask</t>
+          <t>Kojic Acid Turmeric Capsule Serum</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I28" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="I28" s="4" t="n">
-        <v>28</v>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2042,7 +2070,7 @@
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/hypochlorous-acid-peel-mask</t>
+          <t>https://medicube.us/products/kojic-acid-turmeric-capsule-serum</t>
         </is>
       </c>
       <c r="L28" s="2">
@@ -2057,12 +2085,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MB003331</t>
+          <t>MB003238</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hypochlorous Acid Power Soothing Spray: spray calmante com ácido hipocloroso</t>
+          <t>Kojic Acid Turmeric Eye Gel Serum: gel para a área dos olhos com ácido kójico e cafeína</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2071,24 +2099,24 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>159.9</v>
+        <v>203.9</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hypochlorous Acid Power Soothing Spray</t>
+          <t>Kojic Acid Turmeric Eye Gel Serum</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2097,7 +2125,7 @@
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/hypochlorous-acid-power-soothing-spray</t>
+          <t>https://medicube.us/products/kojic-acid-tumeric-eye-gel-serum</t>
         </is>
       </c>
       <c r="L29" s="2">
@@ -2112,12 +2140,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MB003241</t>
+          <t>MB003295</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hypochlorous Acid Rice Body Peel Shot: esfoliante corporal com ácido hipocloroso</t>
+          <t>Kojic Acid Turmeric Gold Jelly Gel Mask: máscara de gel dourada com ácido kójico</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2126,23 +2154,29 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>204.9</v>
+        <v>175.9</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hypochlorous Acid Rice Body Peel Shot</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>Kojic Acid Turmeric Gold Jelly Gel Mask</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1EA</t>
+        </is>
+      </c>
       <c r="H30" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="I30" s="4" t="n"/>
+        <v>5.99</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>6.99</v>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2150,7 +2184,7 @@
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/hypochlorous-acid-rice-body-peel-shot</t>
+          <t>https://medicube.us/products/kojic-acid-turmeric-gold-jelly-gel-mask?variant=41785703465008</t>
         </is>
       </c>
       <c r="L30" s="2">
@@ -2165,12 +2199,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MB003242</t>
+          <t>MB003297</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hypochlorous Acid Rice Peel Shot: peeling facial com ácido hipocloroso e arroz</t>
+          <t>Kojic Acid Turmeric Toner Pad: discos com ácido kójico e cúrcuma (70 discos)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2179,23 +2213,25 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>189.9</v>
+        <v>225.9</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hypochlorous Acid Rice Peel Shot</t>
+          <t>Kojic Acid Turmeric Toner Pad</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="I31" s="4" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>31</v>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2203,7 +2239,7 @@
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/hypochlorous-acid-rice-peel-shot</t>
+          <t>https://medicube.us/products/kojic-acid-tumeric-toner-pad</t>
         </is>
       </c>
       <c r="L31" s="2">
@@ -2218,12 +2254,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MB003235</t>
+          <t>MB003240</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Body Peel Shot: esfoliante corporal com ácido kójico e cúrcuma</t>
+          <t>Kojic Acid Turmeric Vita Capsule Cream: creme em cápsulas com ácido kójico e cúrcuma</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2232,23 +2268,25 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>203.9</v>
+        <v>189.9</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Body Peel Shot</t>
+          <t>Kojic Acid Turmeric Vita Capsule Cream</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="I32" s="4" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>34</v>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2256,7 +2294,7 @@
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/kojic-acid-turmeric-body-peel-shot</t>
+          <t>https://medicube.us/products/kojic-acid-turmeric-vita-capsule-cream</t>
         </is>
       </c>
       <c r="L32" s="2">
@@ -2271,12 +2309,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MB003243</t>
+          <t>MB003231</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Brightening Body Wash: sabonete líquido corporal iluminador</t>
+          <t>Kojic Acid Turmeric Vita Capsule Foam Cleanser: espuma com ácido kójico e cúrcuma</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2285,29 +2323,25 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>160.9</v>
+        <v>145.9</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Brightening Body Wash</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>400ml</t>
-        </is>
-      </c>
+          <t>Kojic Acid Turmeric Vita Capsule Foam Cleanser</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I33" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="I33" s="4" t="n">
-        <v>24</v>
-      </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2315,7 +2349,7 @@
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/kojic-acid-turmeric-brightening-body-wash?variant=43582251532336</t>
+          <t>https://medicube.us/products/kojic-acid-turmeric-vita-capsule-foam-cleanser</t>
         </is>
       </c>
       <c r="L33" s="2">
@@ -2330,12 +2364,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MB003298</t>
+          <t>MB003324</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Capsule Serum: sérum em cápsulas com ácido kójico e cúrcuma</t>
+          <t>Kojic Acid Turmeric Vitamin Gold Jelly Mist Serum: sérum em spray iluminador</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2344,24 +2378,28 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>189.9</v>
+        <v>160.9</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Capsule Serum</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>Kojic Acid Turmeric Vitamin Gold Jelly Mist Serum</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
       <c r="H34" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2370,7 +2408,7 @@
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/kojic-acid-turmeric-capsule-serum</t>
+          <t>https://medicube.us/products/turmeric-vitamin-gold-jelly-mist-serum?variant=43624986148912</t>
         </is>
       </c>
       <c r="L34" s="2">
@@ -2385,12 +2423,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MB003238</t>
+          <t>MB003332</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Eye Gel Serum: gel para a área dos olhos com ácido kójico e cafeína</t>
+          <t>No Cast Just Glow Collagen Sunscreen: protetor solar com colágeno FPS 50</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2399,25 +2437,23 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>203.9</v>
+        <v>159.9</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Eye Gel Serum</t>
+          <t>No Cast Just Glow Collagen Sunscreen</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>28</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="I35" s="4" t="n"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2425,7 +2461,7 @@
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/kojic-acid-tumeric-eye-gel-serum</t>
+          <t>https://medicube.us/products/no-cast-just-glow-collagen-sunscreen</t>
         </is>
       </c>
       <c r="L35" s="2">
@@ -2440,12 +2476,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MB003295</t>
+          <t>MB003310</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Gold Jelly Gel Mask: máscara de gel dourada com ácido kójico</t>
+          <t>PDRN Lip Sleeping Mask: máscara noturna para os lábios com PDRN e karité</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2454,28 +2490,24 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>175.9</v>
+        <v>137.9</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Gold Jelly Gel Mask</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>1EA</t>
-        </is>
-      </c>
+          <t>PDRN Lip Sleeping Mask</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" s="4" t="n">
-        <v>5.99</v>
+        <v>19</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>6.99</v>
+        <v>25</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2484,7 +2516,7 @@
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/kojic-acid-turmeric-gold-jelly-gel-mask?variant=41785703465008</t>
+          <t>https://medicube.us/products/pdrn-lip-sleeping-mask</t>
         </is>
       </c>
       <c r="L36" s="2">
@@ -2499,12 +2531,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MB003236</t>
+          <t>MB003309</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Peel Shot: sérum esfoliante de enxágue com ácido kójico</t>
+          <t>PDRN Pink Caffeine Overnight Wrapping Mask: máscara noturna peel-off com PDRN</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2513,25 +2545,27 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>175.9</v>
+        <v>127.9</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Peel Shot</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+          <t>PDRN Pink Caffeine Overnight Wrapping Mask</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
       <c r="H37" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="I37" s="4" t="n">
-        <v>26</v>
-      </c>
+      <c r="I37" s="4" t="n"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2539,7 +2573,7 @@
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/kojic-acid-turmeric-peel-shot</t>
+          <t>https://medicube.us/products/pdrn-wrapping-mask?variant=42200876679216</t>
         </is>
       </c>
       <c r="L37" s="2">
@@ -2554,12 +2588,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MB003297</t>
+          <t>MB003329</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Toner Pad: discos com ácido kójico e cúrcuma (70 discos)</t>
+          <t>PDRN Pink Collagen Exosome Shot: sérum com microespículas, PDRN e exossomos</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2568,25 +2602,29 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>225.9</v>
+        <v>140.9</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Toner Pad</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>PDRN Pink Collagen Exosome Shot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>MILD(2000)</t>
+        </is>
+      </c>
       <c r="H38" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I38" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="I38" s="4" t="n">
-        <v>31</v>
-      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2594,7 +2632,7 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/kojic-acid-tumeric-toner-pad</t>
+          <t>https://medicube.us/products/pdrn-pink-collagen-exosome-shot?variant=41877873328176</t>
         </is>
       </c>
       <c r="L38" s="2">
@@ -2609,12 +2647,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MB003296</t>
+          <t>MB003307</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Toner: tônico com ácido kójico e cúrcuma para rosto e corpo</t>
+          <t>PDRN Pink Collagen Gel Toner Pad: discos de gel com PDRN, colágeno e niacinamida</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2623,23 +2661,25 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>153.9</v>
+        <v>151.9</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Toner</t>
+          <t>PDRN Pink Collagen Gel Toner Pad</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="I39" s="4" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>33</v>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2647,7 +2687,7 @@
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/kojic-acid-turmeric-toner</t>
+          <t>https://medicube.us/products/pdrn-pink-collagen-gel-toner-pad</t>
         </is>
       </c>
       <c r="L39" s="2">
@@ -2662,12 +2702,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MB003240</t>
+          <t>MB003314</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Vita Capsule Cream: creme em cápsulas com ácido kójico e cúrcuma</t>
+          <t>PDRN Pink Gel Cleanser: gel de limpeza que vira espuma, com PDRN, colágeno e LHA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2680,21 +2720,19 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Vita Capsule Cream</t>
+          <t>PDRN Pink Gel Cleanser</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="I40" s="4" t="n">
-        <v>34</v>
-      </c>
+      <c r="I40" s="4" t="n"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2702,7 +2740,7 @@
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/kojic-acid-turmeric-vita-capsule-cream</t>
+          <t>https://medicube.us/products/pdrn-gel-cleanser</t>
         </is>
       </c>
       <c r="L40" s="2">
@@ -2717,12 +2755,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MB003231</t>
+          <t>MB003230</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Vita Capsule Foam Cleanser: espuma com ácido kójico e cúrcuma</t>
+          <t>PDRN Pink Glutathione Capsule Foam Cleanser: espuma com PDRN e glutationa</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2731,16 +2769,16 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>145.9</v>
+        <v>144.9</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Vita Capsule Foam Cleanser</t>
+          <t>PDRN Pink Glutathione Capsule Foam Cleanser</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -2757,7 +2795,7 @@
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/kojic-acid-turmeric-vita-capsule-foam-cleanser</t>
+          <t>https://medicube.us/products/pdrn-pink-glutathione-capsule-foam-cleanser</t>
         </is>
       </c>
       <c r="L41" s="2">
@@ -2772,12 +2810,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MB003324</t>
+          <t>MB003308</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Vitamin Gold Jelly Mist Serum: sérum em spray iluminador</t>
+          <t>PDRN Pink Niacinamide Milky Toner: tônico leitoso com PDRN, ceramida e peptídeos</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2786,29 +2824,23 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>160.9</v>
+        <v>121.9</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Vitamin Gold Jelly Mist Serum</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>100ml</t>
-        </is>
-      </c>
+          <t>PDRN Pink Niacinamide Milky Toner</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>28</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I42" s="4" t="n"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2816,7 +2848,7 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/turmeric-vitamin-gold-jelly-mist-serum?variant=43624986148912</t>
+          <t>https://medicube.us/products/pdrn-pink-niacinamide-milky-toner</t>
         </is>
       </c>
       <c r="L42" s="2">
@@ -2831,12 +2863,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MB003332</t>
+          <t>MB003327</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>No Cast Just Glow Collagen Sunscreen: protetor solar com colágeno FPS 50</t>
+          <t>PDRN Pink One Day Serum: ampola de dose única com PDRN, colágeno e glutationa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2845,23 +2877,25 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>159.9</v>
+        <v>137.9</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>No Cast Just Glow Collagen Sunscreen</t>
+          <t>PDRN Pink One Day Serum</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="I43" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="I43" s="4" t="n"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2869,7 +2903,7 @@
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/no-cast-just-glow-collagen-sunscreen</t>
+          <t>https://medicube.us/products/pdrn-pink-one-day-serum</t>
         </is>
       </c>
       <c r="L43" s="2">
@@ -2884,12 +2918,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MB003310</t>
+          <t>MB003313</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PDRN Lip Sleeping Mask: máscara noturna para os lábios com PDRN e karité</t>
+          <t>PDRN Pink Peptide Eye Cream: creme para a área dos olhos com PDRN e retinol</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2898,24 +2932,24 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>137.9</v>
+        <v>188.9</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PDRN Lip Sleeping Mask</t>
+          <t>PDRN Pink Peptide Eye Cream</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" s="4" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2924,7 +2958,7 @@
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-lip-sleeping-mask</t>
+          <t>https://medicube.us/products/pdrn-pink-peptide-eye-cream</t>
         </is>
       </c>
       <c r="L44" s="2">
@@ -2939,12 +2973,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MB003309</t>
+          <t>MB003328</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PDRN Pink Caffeine Overnight Wrapping Mask: máscara noturna peel-off com PDRN</t>
+          <t>PDRN Pink Peptide Toner: tônico com PDRN, niacinamida e peptídeos 250 ml</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2953,31 +2987,35 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>127.9</v>
+        <v>152.9</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>[Subscr.] PDRN Pink Caffeine Overnight Wrapping Mask</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+          <t>PDRN Pink Peptide Toner</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
       <c r="H45" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I45" s="4" t="n"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/subscr-pdrn-pink-caffeine-overnight-wrapping-mask</t>
+          <t>https://medicube.us/products/pdrn-pink-peptide-toner-1?variant=42090422829104</t>
         </is>
       </c>
       <c r="L45" s="2">
@@ -2992,12 +3030,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MB003330</t>
+          <t>MB003227</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PDRN Pink Collagen Capsule Cream: creme em cápsulas com PDRN e colágeno 55 g</t>
+          <t>PDRN Pink Tension Up Mask: máscara tensora para queixo e contorno com PDRN</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3006,23 +3044,25 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>169.9</v>
+        <v>188.9</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>[Subscr.] PDRN Pink Collagen Capsule Cream</t>
+          <t>PDRN Pink Tension Up Mask</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="I46" s="4" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>28</v>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3030,7 +3070,7 @@
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/subscr-pdrn-pink-collagen-capsule-cream</t>
+          <t>https://medicube.us/products/pdrn-pink-tension-up-mask</t>
         </is>
       </c>
       <c r="L46" s="2">
@@ -3045,12 +3085,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MB003329</t>
+          <t>MB003311</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PDRN Pink Collagen Exosome Shot: sérum com microespículas, PDRN e exossomos</t>
+          <t>PDRN Pink Vita Coating Sheet Mask: máscara em folha com PDRN e vitamina B12</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3059,28 +3099,24 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>140.9</v>
+        <v>174.9</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>PDRN Pink Collagen Exosome Shot</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>MILD(2000)</t>
-        </is>
-      </c>
+          <t>PDRN Pink Vita Coating Sheet Mask</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3089,7 +3125,7 @@
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-pink-collagen-exosome-shot?variant=41877873328176</t>
+          <t>https://medicube.us/products/pdrn-pink-vita-coating-sheet-mask</t>
         </is>
       </c>
       <c r="L47" s="2">
@@ -3104,12 +3140,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MB003307</t>
+          <t>MB003266</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PDRN Pink Collagen Gel Toner Pad: discos de gel com PDRN, colágeno e niacinamida</t>
+          <t>Red Body Peeling Shot Cleanser: spray esfoliante corporal com 32% de ácidos 110 g</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3118,25 +3154,23 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>151.9</v>
+        <v>174.9</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>PDRN Pink Collagen Gel Toner Pad</t>
+          <t>Red Body Peeling Shot Cleanser</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="I48" s="4" t="n">
-        <v>33</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="I48" s="4" t="n"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3144,7 +3178,7 @@
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-pink-collagen-gel-toner-pad</t>
+          <t>https://medicube.us/products/red-body-peeling-shot-cleanser</t>
         </is>
       </c>
       <c r="L48" s="2">
@@ -3159,12 +3193,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MB003325</t>
+          <t>MB003252</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PDRN Pink Collagen Glow Jelly Mist Serum: sérum em bruma com PDRN e colágeno</t>
+          <t>Red Body Wash: sabonete líquido corporal com ácido salicílico e niacinamida 400 ml</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3173,37 +3207,37 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>151.9</v>
+        <v>160.9</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PDRN Pink Collagen Glow Jelly Mist Serum</t>
+          <t>Red Body Wash</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>SINGLE</t>
         </is>
       </c>
       <c r="H49" s="4" t="n">
         <v>22</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-jelly-mist?variant=43624682881072</t>
+          <t>https://medicube.us/products/red-body-wash?variant=39919971205168</t>
         </is>
       </c>
       <c r="L49" s="2">
@@ -3218,12 +3252,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MB003239</t>
+          <t>MB003258</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PDRN Pink Collagen Glow Jelly Serum: sérum em gel com PDRN, colágeno e niacinamida</t>
+          <t>Red Centellaca Mask: máscara calmante em 3 passos com centella e niacinamida</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3232,28 +3266,28 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>174.9</v>
+        <v>35.9</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>PDRN Pink Collagen Glow Jelly Mist Serum</t>
+          <t>Red Centellaca Mask</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>2 MASKS</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -3262,7 +3296,7 @@
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-jelly-mist?variant=43624682881072</t>
+          <t>https://medicube.us/products/medicube-red-centellaca-mask-2ea?variant=40999720943664</t>
         </is>
       </c>
       <c r="L50" s="2">
@@ -3277,12 +3311,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MB003314</t>
+          <t>MB003265</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PDRN Pink Gel Cleanser: gel de limpeza que vira espuma, com PDRN, colágeno e LHA</t>
+          <t>Red Clear Capsule Body Lotion: loção corporal com cápsulas e ácidos 230 ml</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3291,23 +3325,25 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>189.9</v>
+        <v>160.9</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>PDRN Pink Gel Cleanser</t>
+          <t>Red Clear Capsule Body Lotion</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="I51" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>23</v>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3315,7 +3351,7 @@
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-gel-cleanser</t>
+          <t>https://medicube.us/products/red-clear-capsule-body-lotion</t>
         </is>
       </c>
       <c r="L51" s="2">
@@ -3330,12 +3366,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MB003316</t>
+          <t>MB003262</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PDRN Pink Glow Full Set: tônico, sérum e creme com PDRN</t>
+          <t>Red Foam Cleanser: espuma de limpeza com 0,45% de ácido salicílico 120 ml</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3344,37 +3380,33 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>655.9</v>
+        <v>144.9</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>PDRN Pink Glow Full Set</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Rose PDRN (Vegan)</t>
-        </is>
-      </c>
+          <t>Red Foam Cleanser</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" s="4" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>95.98</v>
+        <v>22</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-exosome-set?variant=41729848508464</t>
+          <t>https://medicube.us/products/red-foam-cleanser-120-ml</t>
         </is>
       </c>
       <c r="L52" s="2">
@@ -3389,12 +3421,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MB003230</t>
+          <t>MB003247</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PDRN Pink Glutathione Capsule Foam Cleanser: espuma com PDRN e glutationa</t>
+          <t>Red Glow Body Essentials: rotina corporal com esfoliante, sabonete e loção</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3403,33 +3435,33 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>144.9</v>
+        <v>176.9</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>PDRN Pink Glutathione Capsule Foam Cleanser</t>
+          <t>Red Glow Body Essentials</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" s="4" t="n">
-        <v>20</v>
+        <v>24.3</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-pink-glutathione-capsule-foam-cleanser</t>
+          <t>https://medicube.us/products/red-glow-body-essentials</t>
         </is>
       </c>
       <c r="L53" s="2">
@@ -3444,12 +3476,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MB003308</t>
+          <t>MB003248</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PDRN Pink Niacinamide Milky Toner: tônico leitoso com PDRN, ceramida e peptídeos</t>
+          <t>Red Line Full Set: rotina facial de 4 passos para pele oleosa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3458,23 +3490,29 @@
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>121.9</v>
+        <v>802.9</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>PDRN Pink Niacinamide Milky Toner</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>Red Line Full Set</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Red Line Full Set</t>
+        </is>
+      </c>
       <c r="H54" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="I54" s="4" t="n"/>
+        <v>110</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>165</v>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3482,7 +3520,7 @@
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-pink-niacinamide-milky-toner</t>
+          <t>https://medicube.us/products/red-line-full-set?variant=41597301588016</t>
         </is>
       </c>
       <c r="L54" s="2">
@@ -3497,12 +3535,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MB003327</t>
+          <t>MB003246</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PDRN Pink One Day Serum: ampola de dose única com PDRN, colágeno e glutationa</t>
+          <t>Red Line Ultimate Face &amp; Body Care Set: rotina Red completa para rosto e corpo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3511,33 +3549,37 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>137.9</v>
+        <v>1255.9</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>PDRN Pink One Day Serum</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
+          <t>Red Line Ultimate Face &amp; Body Care Set</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Red Line Ultimate Face &amp; Body Care Set</t>
+        </is>
+      </c>
       <c r="H55" s="4" t="n">
-        <v>19</v>
+        <v>172.2</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>22</v>
+        <v>246</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-pink-one-day-serum</t>
+          <t>https://medicube.us/products/red-line-ultimate-face-body-care-set?variant=41597303423024</t>
         </is>
       </c>
       <c r="L55" s="2">
@@ -3552,12 +3594,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MB003326</t>
+          <t>MB003264</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PDRN Pink Peptide Cream: hidratante leve com PDRN e ácido hialurônico 50 ml</t>
+          <t>Red Succinic Acid Panthenol Pads: discos de tônico para pele oleosa (70 discos)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3566,25 +3608,29 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>188.9</v>
+        <v>180.9</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>PDRN Pink Peptide Eye Cream</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+          <t>Red Succinic Acid Panthenol Pads</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
       <c r="H56" s="4" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="I56" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="I56" s="4" t="n">
-        <v>28</v>
-      </c>
       <c r="J56" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3592,7 +3638,7 @@
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-pink-peptide-eye-cream</t>
+          <t>https://medicube.us/products/red-succinic-acid-panthenol-pads?variant=41268490960944</t>
         </is>
       </c>
       <c r="L56" s="2">
@@ -3607,12 +3653,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MB003313</t>
+          <t>MB003269</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PDRN Pink Peptide Eye Cream: creme para a área dos olhos com PDRN e retinol</t>
+          <t>Retinol NMN Boosting Serum: sérum de retinol com NMN e peptídeos</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3621,25 +3667,25 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>188.9</v>
+        <v>174.9</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PDRN Pink Peptide Eye Cream</t>
+          <t>Retinol NMN Boosting Serum</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I57" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="I57" s="4" t="n">
-        <v>28</v>
-      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3647,7 +3693,7 @@
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-pink-peptide-eye-cream</t>
+          <t>https://medicube.us/products/retinol-nmn-boosting-serum</t>
         </is>
       </c>
       <c r="L57" s="2">
@@ -3662,12 +3708,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MB003312</t>
+          <t>MB003234</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PDRN Pink Peptide Serum: sérum de PDRN com peptídeos e niacinamida 30 ml</t>
+          <t>Rosemary PDRN Cooling Thickening Shampoo: shampoo refrescante de alecrim e PDRN</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3676,28 +3722,24 @@
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>133.9</v>
+        <v>188.9</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ultra Light PDRN Pink Peptide Serum</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Light PDRN (30ml)</t>
-        </is>
-      </c>
+          <t>Rosemary PDRN Cooling Thickening Shampoo</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" s="4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -3706,7 +3748,7 @@
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/ultra-light-pdrn-pink-peptide-serum?variant=43308557795376</t>
+          <t>https://medicube.us/products/rosemary-pdrn-cooling-thickening-shampoo</t>
         </is>
       </c>
       <c r="L58" s="2">
@@ -3721,12 +3763,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MB003328</t>
+          <t>MB003233</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PDRN Pink Peptide Toner: tônico com PDRN, niacinamida e peptídeos 250 ml</t>
+          <t>Rosemary PDRN Hair &amp; Scalp Conditioner: condicionador de alecrim com PDRN</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3735,35 +3777,33 @@
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>152.9</v>
+        <v>188.9</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>PDRN Pink Peptide Toner</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Rose</t>
-        </is>
-      </c>
+          <t>Rosemary PDRN Hair &amp; Scalp Conditioner</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="I59" s="4" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>31</v>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-pink-peptide-toner-1?variant=42090422829104</t>
+          <t>https://medicube.us/products/rosemary-pdrn-hair-scalp-conditioner</t>
         </is>
       </c>
       <c r="L59" s="2">
@@ -3778,12 +3818,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MB003227</t>
+          <t>MB003232</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PDRN Pink Tension Up Mask: máscara tensora para queixo e contorno com PDRN</t>
+          <t>Rosemary PDRN Scalp Serum: sérum para couro cabeludo com alecrim e PDRN</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3792,25 +3832,25 @@
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>188.9</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>PDRN Pink Tension Up Mask</t>
+          <t>Rosemary PDRN Scalp Serum</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="I60" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="I60" s="4" t="n">
-        <v>28</v>
-      </c>
       <c r="J60" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3818,7 +3858,7 @@
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-pink-tension-up-mask</t>
+          <t>https://medicube.us/products/rosemary-pdrn-scalp-serum</t>
         </is>
       </c>
       <c r="L60" s="2">
@@ -3833,12 +3873,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MB003311</t>
+          <t>MB003277</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PDRN Pink Vita Coating Sheet Mask: máscara em folha com PDRN e vitamina B12</t>
+          <t>Super Cica Calming Mask: máscara em folha calmante com 7 tipos de centella</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3847,24 +3887,28 @@
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>174.9</v>
+        <v>42.9</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>PDRN Pink Vita Coating Sheet Mask</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
+          <t>Super Cica Calming Mask</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2 MASKS</t>
+        </is>
+      </c>
       <c r="H61" s="4" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3873,7 +3917,7 @@
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-pink-vita-coating-sheet-mask</t>
+          <t>https://medicube.us/products/super-cica-calming-mask?variant=40999721435184</t>
         </is>
       </c>
       <c r="L61" s="2">
@@ -3888,12 +3932,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MB003284</t>
+          <t>MB003274</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pore Care Duo: sérum Zero Pore One-day 30 ml + creme Zero Pore One-day 50 ml</t>
+          <t>Super Cica Daily Quick Masks: 30 máscaras calmantes de centella</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3902,24 +3946,28 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>328.9</v>
+        <v>232.9</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pore Care Duo</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>Super Cica Daily Quick Masks</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
       <c r="H62" s="4" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3928,7 +3976,7 @@
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/new-pore-care-duo-set</t>
+          <t>https://medicube.us/products/super-cica-daily-quick-mask</t>
         </is>
       </c>
       <c r="L62" s="2">
@@ -3943,12 +3991,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MB003266</t>
+          <t>MB003276</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Red Body Peeling Shot Cleanser: spray esfoliante corporal com 32% de ácidos 110 g</t>
+          <t>Super Cica Exfoliating Cleansing Balm: bálsamo de limpeza com centella 100 ml</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3957,23 +4005,25 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>174.9</v>
+        <v>137.9</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Red Body Peeling Shot Cleanser</t>
+          <t>Super Cica Exfoliating Cleansing Balm</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I63" s="4" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>35</v>
+      </c>
       <c r="J63" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3981,7 +4031,7 @@
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/red-body-peeling-shot-cleanser</t>
+          <t>https://medicube.us/products/super-cica-exfoliating-cleansing-balm-vegan</t>
         </is>
       </c>
       <c r="L63" s="2">
@@ -3996,12 +4046,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MB003252</t>
+          <t>MB003275</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Red Body Wash: sabonete líquido corporal com ácido salicílico e niacinamida 400 ml</t>
+          <t>Super Cica Toner: tônico calmante de centella sem álcool 210 ml</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4010,28 +4060,24 @@
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>160.9</v>
+        <v>115.9</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Red Body Wash</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>SINGLE</t>
-        </is>
-      </c>
+          <t>Super Cica Toner</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -4040,7 +4086,7 @@
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/red-body-wash?variant=39919971205168</t>
+          <t>https://medicube.us/products/super-cica-water-in-toner</t>
         </is>
       </c>
       <c r="L64" s="2">
@@ -4055,12 +4101,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MB003258</t>
+          <t>MB003293</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Red Centellaca Mask: máscara calmante em 3 passos com centella e niacinamida</t>
+          <t>TXA Niacinamide Capsule Cream: creme em cápsulas com ácido tranexâmico</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4069,28 +4115,28 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>35.9</v>
+        <v>188.9</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Red Centellaca Mask</t>
+          <t>TXA Niacinamide Capsule Cream</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2 MASKS</t>
+          <t>SINGLE</t>
         </is>
       </c>
       <c r="H65" s="4" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -4099,7 +4145,7 @@
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/medicube-red-centellaca-mask-2ea?variant=40999720943664</t>
+          <t>https://medicube.us/products/txa-niacinamide-capsule-cream?variant=41980200288304</t>
         </is>
       </c>
       <c r="L65" s="2">
@@ -4114,12 +4160,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MB003265</t>
+          <t>MB003294</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Red Clear Capsule Body Lotion: loção corporal com cápsulas e ácidos 230 ml</t>
+          <t>TXA Niacinamide Serum: sérum com 5% de ácido tranexâmico e niacinamida</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4128,24 +4174,24 @@
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>160.9</v>
+        <v>174.9</v>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Red Clear Capsule Body Lotion</t>
+          <t>TXA Niacinamide Serum</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -4154,7 +4200,7 @@
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/red-clear-capsule-body-lotion</t>
+          <t>https://medicube.us/products/txa-niacinamide-serum</t>
         </is>
       </c>
       <c r="L66" s="2">
@@ -4169,12 +4215,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MB003262</t>
+          <t>MB003302</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Red Foam Cleanser: espuma de limpeza com 0,45% de ácido salicílico 120 ml</t>
+          <t>Triple Collagen Cream: creme de colágeno para hidratação e firmeza 50 ml</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4183,24 +4229,28 @@
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>144.9</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Red Foam Cleanser</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
+          <t>Triple Collagen Cream</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
       <c r="H67" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -4209,7 +4259,7 @@
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/red-foam-cleanser-120-ml</t>
+          <t>https://medicube.us/products/deep-erasing-cream?variant=40093603135536</t>
         </is>
       </c>
       <c r="L67" s="2">
@@ -4224,12 +4274,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MB003247</t>
+          <t>MB003301</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Red Glow Body Essentials: rotina corporal com esfoliante, sabonete e loção</t>
+          <t>Triple Collagen Serum: sérum com três tipos de colágeno e niacinamida 55 ml</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4238,33 +4288,33 @@
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>176.9</v>
+        <v>254.9</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Red Glow Body Essentials</t>
+          <t>Triple Collagen Serum</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" s="4" t="n">
-        <v>24.3</v>
+        <v>24</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/red-glow-body-essentials</t>
+          <t>https://medicube.us/products/triple-collagen-serum</t>
         </is>
       </c>
       <c r="L68" s="2">
@@ -4279,12 +4329,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MB003248</t>
+          <t>MB003256</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Red Line Full Set: rotina facial de 4 passos para pele oleosa</t>
+          <t>Triple Collagen Toner: tônico hidratante com 3 tipos de colágeno 140 ml</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4293,29 +4343,23 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>802.9</v>
+        <v>225.9</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Red Line Full Set</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Red Line Full Set</t>
-        </is>
-      </c>
+          <t>Triple Collagen Toner</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" s="4" t="n">
-        <v>110</v>
-      </c>
-      <c r="I69" s="4" t="n">
-        <v>165</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I69" s="4" t="n"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4323,7 +4367,7 @@
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/red-line-full-set?variant=41597301588016</t>
+          <t>https://medicube.us/products/glass-glow-essence-2-0</t>
         </is>
       </c>
       <c r="L69" s="2">
@@ -4338,12 +4382,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MB003246</t>
+          <t>MB003320</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Red Line Ultimate Face &amp; Body Care Set: rotina Red completa para rosto e corpo</t>
+          <t>Zero Exosome Shot: sérum com microespículas para poros 30 ml</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4352,37 +4396,37 @@
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>1255.9</v>
+        <v>145.9</v>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Red Line Ultimate Face &amp; Body Care Set</t>
+          <t>Zero Exosome Shot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Red Line Ultimate Face &amp; Body Care Set</t>
+          <t>MILD(2000)</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>172.2</v>
+        <v>22</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>246</v>
+        <v>24</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/red-line-ultimate-face-body-care-set?variant=41597303423024</t>
+          <t>https://medicube.us/products/exosome-shot?variant=41200136519728</t>
         </is>
       </c>
       <c r="L70" s="2">
@@ -4397,12 +4441,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MB003260</t>
+          <t>MB003286</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Red Serum: sérum calmante com melaleuca para pele oleosa 30 ml</t>
+          <t>Zero Foam Cleanser: espuma de limpeza para poros e oleosidade</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4411,16 +4455,16 @@
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>144.9</v>
+        <v>110.9</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Red Serum</t>
+          <t>Zero Foam Cleanser</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -4428,7 +4472,7 @@
         <v>20</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -4437,7 +4481,7 @@
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/red-serum</t>
+          <t>https://medicube.us/products/zero-foam-cleanser</t>
         </is>
       </c>
       <c r="L71" s="2">
@@ -4452,12 +4496,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MB003264</t>
+          <t>MB003283</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Red Succinic Acid Panthenol Pads: discos de tônico para pele oleosa (70 discos)</t>
+          <t>Zero Line Full Set: discos, sérum e creme Zero Pore para poros</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4466,23 +4510,25 @@
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>180.9</v>
+        <v>480.9</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>[Subscr.] Red Succinic Acid Panthenol Pads</t>
+          <t>Zero Line Full Set</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="I72" s="4" t="n"/>
+        <v>66</v>
+      </c>
+      <c r="I72" s="4" t="n">
+        <v>110</v>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4490,7 +4536,7 @@
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/subscr-red-succinic-acid-panthenol-pads</t>
+          <t>https://medicube.us/products/new-zero-line-full-set</t>
         </is>
       </c>
       <c r="L72" s="2">
@@ -4505,12 +4551,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MB003261</t>
+          <t>MB003321</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Red Toner: tônico calmante com extratos de plantas para pele oleosa 100 ml</t>
+          <t>Zero Pore Blackhead Deep Cleansing Oil: óleo de limpeza para cravos e maquiagem</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4519,24 +4565,28 @@
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>115.9</v>
+        <v>152.9</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Red Toner</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
+          <t>Zero Pore Blackhead Deep Cleansing Oil</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
       <c r="H73" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -4545,7 +4595,7 @@
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/red-toner</t>
+          <t>https://medicube.us/products/zero-pore-blackhead-deep-cleansing-oil?variant=41865193947184</t>
         </is>
       </c>
       <c r="L73" s="2">
@@ -4560,12 +4610,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MB003269</t>
+          <t>MB003291</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Retinol NMN Boosting Serum: sérum de retinol com NMN e peptídeos</t>
+          <t>Zero Pore Capsule Cleansing Foam: espuma de limpeza com microcápsulas para poros</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4574,24 +4624,24 @@
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>174.9</v>
+        <v>110.9</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Retinol NMN Boosting Serum</t>
+          <t>Zero Pore Capsule Cleansing Foam</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -4600,7 +4650,7 @@
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/retinol-nmn-boosting-serum</t>
+          <t>https://medicube.us/products/zero-pore-clear-blue-capsule-facial-deep-cleanser</t>
         </is>
       </c>
       <c r="L74" s="2">
@@ -4615,12 +4665,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MB003234</t>
+          <t>MB003289</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Rosemary PDRN Cooling Thickening Shampoo: shampoo refrescante de alecrim e PDRN</t>
+          <t>Zero Pore Cooling Mask: máscara em folha refrescante para poros</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4629,24 +4679,28 @@
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>188.9</v>
+        <v>18.9</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosemary PDRN Cooling Thickening Shampoo</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr"/>
+          <t>Zero Pore Cooling Mask</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2 MASKS</t>
+        </is>
+      </c>
       <c r="H75" s="4" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -4655,7 +4709,7 @@
       </c>
       <c r="K75" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/rosemary-pdrn-cooling-thickening-shampoo</t>
+          <t>https://medicube.us/products/zero-pore-cooling-mask?variant=40999560871984</t>
         </is>
       </c>
       <c r="L75" s="2">
@@ -4670,12 +4724,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MB003233</t>
+          <t>MB003287</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Rosemary PDRN Hair &amp; Scalp Conditioner: condicionador de alecrim com PDRN</t>
+          <t>Zero Pore One-day Cream: hidratante para poros e pele oleosa 50 ml</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4684,16 +4738,16 @@
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>188.9</v>
+        <v>157.9</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosemary PDRN Hair &amp; Scalp Conditioner</t>
+          <t>Zero Pore One-day Cream</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -4701,7 +4755,7 @@
         <v>26</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -4710,7 +4764,7 @@
       </c>
       <c r="K76" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/rosemary-pdrn-hair-scalp-conditioner</t>
+          <t>https://medicube.us/products/zero-pore-one-day-cream</t>
         </is>
       </c>
       <c r="L76" s="2">
@@ -4725,12 +4779,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MB003232</t>
+          <t>MB003288</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Rosemary PDRN Scalp Serum: sérum para couro cabeludo com alecrim e PDRN</t>
+          <t>Zero Pore One-day Peptide Serum: sérum para poros com 10 peptídeos e ácidos 30 ml</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4739,21 +4793,21 @@
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>80.90000000000001</v>
+        <v>145.9</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rosemary PDRN Scalp Serum</t>
+          <t>Zero Pore One-day Peptide Serum</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" s="4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I77" s="4" t="n">
         <v>26</v>
@@ -4765,7 +4819,7 @@
       </c>
       <c r="K77" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/rosemary-pdrn-scalp-serum</t>
+          <t>https://medicube.us/products/zero-pore-one-day-serum</t>
         </is>
       </c>
       <c r="L77" s="2">
@@ -4780,12 +4834,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MB003315</t>
+          <t>MB003290</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Salmon PDRN Pink Collagen Jelly Gel Mask: máscara de gel com PDRN que muda de cor</t>
+          <t>Zero Pore Toner: tônico esfoliante e hidratante com AHA, BHA, PHA e niacinamida</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4794,29 +4848,23 @@
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>175.9</v>
+        <v>152.9</v>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Salmon PDRN Pink Collagen Jelly Gel Mask</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>1EA</t>
-        </is>
-      </c>
+          <t>Zero Pore Toner</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" s="4" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="I78" s="4" t="n">
-        <v>6.99</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I78" s="4" t="n"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4824,7 +4872,7 @@
       </c>
       <c r="K78" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-pink-collagen-gel-mask?variant=41631127633968</t>
+          <t>https://medicube.us/products/zero-pore-toner</t>
         </is>
       </c>
       <c r="L78" s="2">
@@ -4839,43 +4887,41 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MB003277</t>
+          <t>MB003299</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Super Cica Calming Mask: máscara em folha calmante com 7 tipos de centella</t>
+          <t>Kojic Acid Turmeric Overnight Wrapping Mask: máscara noturna de cúrcuma e ácido kójico</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>42.9</v>
+        <v>139.9</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Super Cica Calming Mask</t>
+          <t>Kojic Acid Turmeric Overnight Wrapping Mask</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2 MASKS</t>
+          <t>SINGLE</t>
         </is>
       </c>
       <c r="H79" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I79" s="4" t="n">
-        <v>12</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="I79" s="4" t="n"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4883,7 +4929,7 @@
       </c>
       <c r="K79" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/super-cica-calming-mask?variant=40999721435184</t>
+          <t>https://medicube.us/products/kojic-acid-tumeric-overnight-wrapping-mask?variant=41896883159088</t>
         </is>
       </c>
       <c r="L79" s="2">
@@ -4898,12 +4944,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MB003274</t>
+          <t>MB003323</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Super Cica Daily Quick Masks: 30 máscaras calmantes de centella</t>
+          <t>Affordable Glass Glow 7-Day Set: rotina de 5 passos com exossomos e colágeno</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4912,28 +4958,28 @@
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>232.9</v>
-      </c>
-      <c r="E80" s="3" t="inlineStr">
+        <v>561.9</v>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Super Cica Daily Quick Masks</t>
+          <t>Affordable Glass Glow 7-Day Skincare Set</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SINGLE</t>
+          <t>Collagen Jelly Cream</t>
         </is>
       </c>
       <c r="H80" s="4" t="n">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>32</v>
+        <v>155</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -4942,7 +4988,7 @@
       </c>
       <c r="K80" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/super-cica-daily-quick-mask</t>
+          <t>https://medicube.us/products/affordable-glass-glow-7-day-skincare-set?variant=41592205738032</t>
         </is>
       </c>
       <c r="L80" s="2">
@@ -4957,12 +5003,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MB003276</t>
+          <t>MB003304</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Super Cica Exfoliating Cleansing Balm: bálsamo de limpeza com centella 100 ml</t>
+          <t>Collagen Glow Bubble Serum: sérum em mousse com 11 tipos de colágeno 100 ml</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4971,24 +5017,24 @@
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>137.9</v>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
+        <v>174.9</v>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Super Cica Exfoliating Cleansing Balm</t>
+          <t>[US ONLY] Collagen Glow Bubble Serum</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" s="4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -4997,7 +5043,7 @@
       </c>
       <c r="K81" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/super-cica-exfoliating-cleansing-balm-vegan</t>
+          <t>https://medicube.us/products/collagen-glow-bubble-serum</t>
         </is>
       </c>
       <c r="L81" s="2">
@@ -5012,12 +5058,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MB003275</t>
+          <t>MB003245</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Super Cica Toner: tônico calmante de centella sem álcool 210 ml</t>
+          <t>Conjunto AGE-R Spotless Radiance</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5026,24 +5072,28 @@
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>115.9</v>
-      </c>
-      <c r="E82" s="3" t="inlineStr">
+        <v>2179.9</v>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Super Cica Toner</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr"/>
+          <t>AGE-R Spotless Radiance Set</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Pink</t>
+        </is>
+      </c>
       <c r="H82" s="4" t="n">
-        <v>16</v>
+        <v>299</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>21</v>
+        <v>529</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -5052,7 +5102,7 @@
       </c>
       <c r="K82" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/super-cica-water-in-toner</t>
+          <t>https://medicube.us/products/age-r-spotless-radiance-set?variant=41769865838640</t>
         </is>
       </c>
       <c r="L82" s="2">
@@ -5067,12 +5117,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MB003293</t>
+          <t>MB003255</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TXA Niacinamide Capsule Cream: creme em cápsulas com ácido tranexâmico</t>
+          <t>Deep Glow Set: tônico, sérum e creme de colágeno em 3 passos</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5081,24 +5131,24 @@
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>188.9</v>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
+        <v>509.9</v>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>[Subscr.] TXA Niacinamide Capsule Cream</t>
+          <t>Deep Glow Set</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" s="4" t="n">
-        <v>27.2</v>
+        <v>70</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -5107,7 +5157,7 @@
       </c>
       <c r="K83" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/subscr-txa-niacinamide-capsule-cream</t>
+          <t>https://medicube.us/products/deep-glow-set-1</t>
         </is>
       </c>
       <c r="L83" s="2">
@@ -5122,12 +5172,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MB003294</t>
+          <t>MB003282</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TXA Niacinamide Serum: sérum com 5% de ácido tranexâmico e niacinamida</t>
+          <t>Deep Vita C Capsule Cream: creme em cápsulas de vitamina C e niacinamida 55 g</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5136,24 +5186,28 @@
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>174.9</v>
-      </c>
-      <c r="E84" s="3" t="inlineStr">
+        <v>169.9</v>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>TXA Niacinamide Serum</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr"/>
+          <t>Deep Vita C Capsule Cream</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
       <c r="H84" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -5162,7 +5216,7 @@
       </c>
       <c r="K84" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/txa-niacinamide-serum</t>
+          <t>https://medicube.us/products/deep-vita-c-capsule-cream?variant=41431644799024</t>
         </is>
       </c>
       <c r="L84" s="2">
@@ -5177,12 +5231,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MB003302</t>
+          <t>MB003242</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Triple Collagen Cream: creme de colágeno para hidratação e firmeza 50 ml</t>
+          <t>Hypochlorous Acid Rice Peel Shot: peeling facial com ácido hipocloroso e arroz</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5191,21 +5245,21 @@
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
+        <v>189.9</v>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>[Subscr.] Triple Collagen Cream</t>
+          <t>Hypochlorous Acid Rice Peel Shot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" s="4" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I85" s="4" t="n"/>
       <c r="J85" t="inlineStr">
@@ -5215,7 +5269,7 @@
       </c>
       <c r="K85" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/subscr-triple-collagen-cream</t>
+          <t>https://medicube.us/products/hypochlorous-acid-rice-peel-shot</t>
         </is>
       </c>
       <c r="L85" s="2">
@@ -5230,12 +5284,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MB003301</t>
+          <t>MB003236</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Triple Collagen Serum: sérum com três tipos de colágeno e niacinamida 55 ml</t>
+          <t>Kojic Acid Turmeric Peel Shot: sérum esfoliante de enxágue com ácido kójico</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5244,16 +5298,16 @@
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>254.9</v>
-      </c>
-      <c r="E86" s="3" t="inlineStr">
+        <v>175.9</v>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Triple Collagen Serum</t>
+          <t>Kojic Acid Turmeric Peel Shot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -5270,7 +5324,7 @@
       </c>
       <c r="K86" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/triple-collagen-serum</t>
+          <t>https://medicube.us/products/kojic-acid-turmeric-peel-shot</t>
         </is>
       </c>
       <c r="L86" s="2">
@@ -5285,12 +5339,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MB003256</t>
+          <t>MB003296</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Triple Collagen Toner: tônico hidratante com 3 tipos de colágeno 140 ml</t>
+          <t>Kojic Acid Turmeric Toner: tônico com ácido kójico e cúrcuma para rosto e corpo</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5299,16 +5353,16 @@
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>225.9</v>
-      </c>
-      <c r="E87" s="3" t="inlineStr">
+        <v>153.9</v>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Triple Collagen Toner</t>
+          <t>Kojic Acid Turmeric Toner</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -5323,7 +5377,7 @@
       </c>
       <c r="K87" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/glass-glow-essence-2-0</t>
+          <t>https://medicube.us/products/kojic-acid-turmeric-toner</t>
         </is>
       </c>
       <c r="L87" s="2">
@@ -5338,12 +5392,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MB003320</t>
+          <t>MB003330</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Zero Exosome Shot: sérum com microespículas para poros 30 ml</t>
+          <t>PDRN Pink Collagen Capsule Cream: creme em cápsulas com PDRN e colágeno 55 g</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5352,28 +5406,28 @@
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>145.9</v>
-      </c>
-      <c r="E88" s="3" t="inlineStr">
+        <v>169.9</v>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Zero Exosome Shot</t>
+          <t>PDRN Pink Collagen Capsule Cream</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>MILD(2000)</t>
+          <t>SINGLE</t>
         </is>
       </c>
       <c r="H88" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -5382,7 +5436,7 @@
       </c>
       <c r="K88" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/exosome-shot?variant=41200136519728</t>
+          <t>https://medicube.us/products/pdrn-pink-collagen-capsule-cream?variant=41902192230448</t>
         </is>
       </c>
       <c r="L88" s="2">
@@ -5397,12 +5451,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MB003286</t>
+          <t>MB003325</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Zero Foam Cleanser: espuma de limpeza para poros e oleosidade</t>
+          <t>PDRN Pink Collagen Glow Jelly Mist Serum: sérum em bruma com PDRN e colágeno</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5411,24 +5465,28 @@
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>110.9</v>
-      </c>
-      <c r="E89" s="3" t="inlineStr">
+        <v>151.9</v>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Zero Foam Cleanser</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr"/>
+          <t>PDRN Pink Collagen Glow Jelly Mist Serum</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
       <c r="H89" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -5437,7 +5495,7 @@
       </c>
       <c r="K89" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/zero-foam-cleanser</t>
+          <t>https://medicube.us/products/pdrn-jelly-mist?variant=43624682881072</t>
         </is>
       </c>
       <c r="L89" s="2">
@@ -5452,12 +5510,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MB003283</t>
+          <t>MB003239</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Zero Line Full Set: discos, sérum e creme Zero Pore para poros</t>
+          <t>PDRN Pink Collagen Glow Jelly Serum: sérum em gel com PDRN, colágeno e niacinamida</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5466,24 +5524,28 @@
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>480.9</v>
-      </c>
-      <c r="E90" s="3" t="inlineStr">
+        <v>174.9</v>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Zero Line Full Set</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr"/>
+          <t>PDRN Pink Collagen Glow Jelly Mist Serum</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
       <c r="H90" s="4" t="n">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -5492,7 +5554,7 @@
       </c>
       <c r="K90" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/new-zero-line-full-set</t>
+          <t>https://medicube.us/products/pdrn-jelly-mist?variant=43624682881072</t>
         </is>
       </c>
       <c r="L90" s="2">
@@ -5507,12 +5569,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MB003321</t>
+          <t>MB003316</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Zero Pore Blackhead Deep Cleansing Oil: óleo de limpeza para cravos e maquiagem</t>
+          <t>PDRN Pink Glow Full Set: tônico, sérum e creme com PDRN</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5521,31 +5583,37 @@
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>152.9</v>
-      </c>
-      <c r="E91" s="3" t="inlineStr">
+        <v>655.9</v>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>[Subscr.] Zero Pore Blackhead Deep Cleansing Oil</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr"/>
+          <t>PDRN Pink Glow Full Set</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Rose PDRN (Vegan)</t>
+        </is>
+      </c>
       <c r="H91" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="I91" s="4" t="n"/>
+        <v>90</v>
+      </c>
+      <c r="I91" s="4" t="n">
+        <v>95.98</v>
+      </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K91" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/subscr-zero-pore-blackhead-deep-cleansing-oil</t>
+          <t>https://medicube.us/products/pdrn-exosome-set?variant=41729848508464</t>
         </is>
       </c>
       <c r="L91" s="2">
@@ -5560,12 +5628,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MB003285</t>
+          <t>MB003326</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Zero Pore Blackhead Mud Mask: máscara de argila para cravos que seca em 3 minutos 100 g</t>
+          <t>PDRN Pink Peptide Cream: hidratante leve com PDRN e ácido hialurônico 50 ml</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5574,28 +5642,24 @@
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>110.9</v>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
+        <v>188.9</v>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Zero Pore Blackhead Deep Cleansing Oil</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Deep Pore (+Zero Mud Mask)</t>
-        </is>
-      </c>
+          <t>PDRN Pink Peptide Eye Cream</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" s="4" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -5604,7 +5668,7 @@
       </c>
       <c r="K92" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/zero-pore-blackhead-deep-cleansing-oil?variant=41865193979952</t>
+          <t>https://medicube.us/products/pdrn-pink-peptide-eye-cream</t>
         </is>
       </c>
       <c r="L92" s="2">
@@ -5619,12 +5683,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MB003291</t>
+          <t>MB003312</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Zero Pore Capsule Cleansing Foam: espuma de limpeza com microcápsulas para poros</t>
+          <t>PDRN Pink Peptide Serum: sérum de PDRN com peptídeos e niacinamida 30 ml</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5633,24 +5697,28 @@
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>110.9</v>
-      </c>
-      <c r="E93" s="3" t="inlineStr">
+        <v>133.9</v>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Zero Pore Capsule Cleansing Foam</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr"/>
+          <t>Ultra Light PDRN Pink Peptide Serum</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Light PDRN (30ml)</t>
+        </is>
+      </c>
       <c r="H93" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -5659,7 +5727,7 @@
       </c>
       <c r="K93" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/zero-pore-clear-blue-capsule-facial-deep-cleanser</t>
+          <t>https://medicube.us/products/ultra-light-pdrn-pink-peptide-serum?variant=43308557795376</t>
         </is>
       </c>
       <c r="L93" s="2">
@@ -5674,12 +5742,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MB003289</t>
+          <t>MB003284</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Zero Pore Cooling Mask: máscara em folha refrescante para poros</t>
+          <t>Pore Care Duo: sérum Zero Pore One-day 30 ml + creme Zero Pore One-day 50 ml</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5688,28 +5756,24 @@
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
+        <v>328.9</v>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Zero Pore Cooling Mask</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>2 MASKS</t>
-        </is>
-      </c>
+          <t>Pore Care Duo</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" s="4" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -5718,7 +5782,7 @@
       </c>
       <c r="K94" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/zero-pore-cooling-mask?variant=40999560871984</t>
+          <t>https://medicube.us/products/new-pore-care-duo-set</t>
         </is>
       </c>
       <c r="L94" s="2">
@@ -5733,12 +5797,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MB003287</t>
+          <t>MB003260</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Zero Pore One-day Cream: hidratante para poros e pele oleosa 50 ml</t>
+          <t>Red Serum: sérum calmante com melaleuca para pele oleosa 30 ml</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5747,25 +5811,25 @@
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>157.9</v>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
+        <v>144.9</v>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Zero Pore One-day Cream</t>
+          <t>Red Serum</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I95" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="I95" s="4" t="n">
-        <v>34</v>
-      </c>
       <c r="J95" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -5773,7 +5837,7 @@
       </c>
       <c r="K95" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/zero-pore-one-day-cream</t>
+          <t>https://medicube.us/products/red-serum</t>
         </is>
       </c>
       <c r="L95" s="2">
@@ -5788,12 +5852,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MB003288</t>
+          <t>MB003261</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Zero Pore One-day Peptide Serum: sérum para poros com 10 peptídeos e ácidos 30 ml</t>
+          <t>Red Toner: tônico calmante com extratos de plantas para pele oleosa 100 ml</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5802,24 +5866,24 @@
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>145.9</v>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
+        <v>115.9</v>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Zero Pore One-day Peptide Serum</t>
+          <t>Red Toner</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -5828,7 +5892,7 @@
       </c>
       <c r="K96" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/zero-pore-one-day-serum</t>
+          <t>https://medicube.us/products/red-toner</t>
         </is>
       </c>
       <c r="L96" s="2">
@@ -5843,12 +5907,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MB003322</t>
+          <t>MB003315</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Zero Pore Pads: discos esfoliantes para poros com AHA e BHA (70 discos)</t>
+          <t>Salmon PDRN Pink Collagen Jelly Gel Mask: máscara de gel com PDRN que muda de cor</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5857,23 +5921,29 @@
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>152.9</v>
-      </c>
-      <c r="E97" s="3" t="inlineStr">
+        <v>175.9</v>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>[Subscr.] Zero Pore Pads</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr"/>
+          <t>Salmon PDRN Pink Collagen Jelly Gel Mask</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>1EA</t>
+        </is>
+      </c>
       <c r="H97" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="I97" s="4" t="n"/>
+        <v>5.99</v>
+      </c>
+      <c r="I97" s="4" t="n">
+        <v>6.99</v>
+      </c>
       <c r="J97" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -5881,7 +5951,7 @@
       </c>
       <c r="K97" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/subscr-zero-pore-pads</t>
+          <t>https://medicube.us/products/pdrn-pink-collagen-gel-mask?variant=41631127633968</t>
         </is>
       </c>
       <c r="L97" s="2">
@@ -5896,12 +5966,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MB003290</t>
+          <t>MB003285</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Zero Pore Toner: tônico esfoliante e hidratante com AHA, BHA, PHA e niacinamida</t>
+          <t>Zero Pore Blackhead Mud Mask: máscara de argila para cravos que seca em 3 minutos 100 g</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5910,23 +5980,29 @@
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>152.9</v>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
+        <v>110.9</v>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Zero Pore Toner</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr"/>
+          <t>Zero Pore Blackhead Deep Cleansing Oil</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Deep Pore (+Zero Mud Mask)</t>
+        </is>
+      </c>
       <c r="H98" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="I98" s="4" t="n"/>
+        <v>37</v>
+      </c>
+      <c r="I98" s="4" t="n">
+        <v>49</v>
+      </c>
       <c r="J98" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -5934,7 +6010,7 @@
       </c>
       <c r="K98" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/zero-pore-toner</t>
+          <t>https://medicube.us/products/zero-pore-blackhead-deep-cleansing-oil?variant=41865193979952</t>
         </is>
       </c>
       <c r="L98" s="2">
@@ -5949,37 +6025,43 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MB003299</t>
+          <t>MB003322</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Overnight Wrapping Mask: máscara noturna de cúrcuma e ácido kójico</t>
+          <t>Zero Pore Pads: discos esfoliantes para poros com AHA e BHA (70 discos)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>139.9</v>
-      </c>
-      <c r="E99" s="3" t="inlineStr">
+        <v>152.9</v>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>[Subscr.] Kojic Acid Turmeric Overnight Wrapping Mask</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr"/>
+          <t>Zero Pore Pads</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
       <c r="H99" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="I99" s="4" t="n"/>
+      <c r="I99" s="4" t="n">
+        <v>31</v>
+      </c>
       <c r="J99" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -5987,7 +6069,7 @@
       </c>
       <c r="K99" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/subscr-kojic-acid-turmeric-overnight-wrapping-mask</t>
+          <t>https://medicube.us/products/zero-pore-pad-1?variant=40542710825008</t>
         </is>
       </c>
       <c r="L99" s="2">
@@ -6002,12 +6084,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MB003273</t>
+          <t>MB003251</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Creme em Cápsulas AGE-R Glutathione Glow</t>
+          <t>Máscara Deep Vita C</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6016,16 +6098,16 @@
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>174.9</v>
-      </c>
-      <c r="E100" s="7" t="inlineStr">
+        <v>137.9</v>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>AGE-R Glutathione Glow Serum</t>
+          <t>Deep Vita C Daily Quick Masks</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -6033,7 +6115,7 @@
         <v>24</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -6042,7 +6124,7 @@
       </c>
       <c r="K100" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/age-r-glutathione-glow-serum</t>
+          <t>https://medicube.us/products/deep-vita-c-daily-quick-masks</t>
         </is>
       </c>
       <c r="L100" s="2">
@@ -6057,12 +6139,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MB003251</t>
+          <t>MB003272</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Máscara Deep Vita C</t>
+          <t>Sérum em gel booster</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6071,24 +6153,24 @@
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>137.9</v>
-      </c>
-      <c r="E101" s="7" t="inlineStr">
+        <v>101.9</v>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Deep Vita C Patch</t>
+          <t>PDRN Booster Gel</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I101" s="4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -6097,7 +6179,7 @@
       </c>
       <c r="K101" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/deep-vita-c-patch</t>
+          <t>https://medicube.us/products/pdrn-booster-gel</t>
         </is>
       </c>
       <c r="L101" s="2">
@@ -6112,38 +6194,38 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MB003272</t>
+          <t>MB003279</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sérum em gel booster</t>
+          <t>Adesivo Deep Vita C</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>101.9</v>
-      </c>
-      <c r="E102" s="7" t="inlineStr">
+        <v>109</v>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>PDRN Booster Gel</t>
+          <t>Deep Vita C Patch</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -6152,7 +6234,7 @@
       </c>
       <c r="K102" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-booster-gel</t>
+          <t>https://medicube.us/products/deep-vita-c-patch</t>
         </is>
       </c>
       <c r="L102" s="2">
@@ -6167,12 +6249,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MB003279</t>
+          <t>MB003271</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Adesivo Deep Vita C</t>
+          <t>Creme Vita K</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6181,24 +6263,28 @@
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="E103" s="7" t="inlineStr">
+        <v>73</v>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Deep Vita C Patch</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr"/>
+          <t>Deep Vita C Capsule Cream</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
       <c r="H103" s="4" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I103" s="4" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -6207,7 +6293,7 @@
       </c>
       <c r="K103" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/deep-vita-c-patch</t>
+          <t>https://medicube.us/products/deep-vita-c-capsule-cream?variant=41431644799024</t>
         </is>
       </c>
       <c r="L103" s="2">
@@ -6222,12 +6308,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MB003271</t>
+          <t>MB003987</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Creme Vita K</t>
+          <t>Kit PDRN Colágeno Rosa Glow</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6236,24 +6322,28 @@
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="E104" s="7" t="inlineStr">
+        <v>656.9</v>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Deep Vita C Patch</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr"/>
+          <t>Ultimate PDRN 2X Glow Set</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Pink</t>
+        </is>
+      </c>
       <c r="H104" s="4" t="n">
-        <v>19</v>
+        <v>279</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>21</v>
+        <v>351</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -6262,7 +6352,7 @@
       </c>
       <c r="K104" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/deep-vita-c-patch</t>
+          <t>https://medicube.us/products/ultimate-pdrn-2x-glow-set?variant=43604705345584</t>
         </is>
       </c>
       <c r="L104" s="2">
@@ -6277,12 +6367,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MB003987</t>
+          <t>MB003259</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Kit PDRN Colágeno Rosa Glow</t>
+          <t>Red Cream</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6291,28 +6381,24 @@
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>656.9</v>
-      </c>
-      <c r="E105" s="7" t="inlineStr">
+        <v>114</v>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ultimate PDRN 2X Glow Set</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Pink</t>
-        </is>
-      </c>
+          <t>3H Daily Relief Cream</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" s="4" t="n">
-        <v>279</v>
+        <v>26</v>
       </c>
       <c r="I105" s="4" t="n">
-        <v>351</v>
+        <v>31</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -6321,7 +6407,7 @@
       </c>
       <c r="K105" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/ultimate-pdrn-2x-glow-set?variant=43604705345584</t>
+          <t>https://medicube.us/products/3h-daily-relief-cream</t>
         </is>
       </c>
       <c r="L105" s="2">
@@ -6336,12 +6422,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MB003259</t>
+          <t>MB003253</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Red Cream</t>
+          <t>Sérum Iluminador com Glutationa AGE-R</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6350,25 +6436,25 @@
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>114</v>
-      </c>
-      <c r="E106" s="7" t="inlineStr">
+        <v>145.9</v>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>3H Daily Relief Cream</t>
+          <t>AGE-R Glutathione Glow Serum</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I106" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="I106" s="4" t="n">
-        <v>31</v>
-      </c>
       <c r="J106" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -6376,7 +6462,7 @@
       </c>
       <c r="K106" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/3h-daily-relief-cream</t>
+          <t>https://medicube.us/products/age-r-glutathione-glow-serum</t>
         </is>
       </c>
       <c r="L106" s="2">
@@ -6391,57 +6477,31 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MB003253</t>
+          <t>MB003273</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Sérum Iluminador com Glutationa AGE-R</t>
+          <t>Creme em Cápsulas AGE-R Glutathione Glow</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>145.9</v>
-      </c>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>AGE-R Glutathione Glow Serum</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I107" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K107" s="5" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/age-r-glutathione-glow-serum</t>
-        </is>
-      </c>
-      <c r="L107" s="2">
-        <f>ROUND(H107*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
-        <v/>
-      </c>
-      <c r="M107" s="6">
-        <f>IF(OR(D107="",L107=""),"",D107/L107-1)</f>
-        <v/>
-      </c>
+        <v>174.9</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="n"/>
+      <c r="I107" s="4" t="n"/>
+      <c r="L107" s="2" t="n"/>
+      <c r="M107" s="6" t="n"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6695,11 +6755,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId106"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId107"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId106"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6710,7 +6769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H308"/>
+  <dimension ref="A1:H254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -14983,148 +15042,194 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>[Subscr.] AGE-R Glutathione Glow Serum</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr"/>
+          <t>[Tati's Exclusive] All About Glow Set</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Collagen Wrapping Mask Set</t>
+        </is>
+      </c>
       <c r="C249" t="n">
-        <v>26</v>
+        <v>540</v>
+      </c>
+      <c r="D249" t="n">
+        <v>575</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F249" t="inlineStr"/>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>PMEUS59003A00</t>
+          <t>KUSMEA00793</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/subscr-age-r-glutathione-glow-serum</t>
+          <t>https://medicube.us/products/tatis-exclusive-all-about-glow-set?variant=41738371006512</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>[Subscr.] Azelaic Acid 16 Calming Serum</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr"/>
+          <t>[Tati's Exclusive] All About Glow Set</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>PDRN Gel Mask Set</t>
+        </is>
+      </c>
       <c r="C250" t="n">
-        <v>26</v>
+        <v>540</v>
+      </c>
+      <c r="D250" t="n">
+        <v>574.96</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr"/>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>PMEKR43004R00</t>
+          <t>KUSMEA00844</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/subscr-azelaic-acid-16-calming-serum</t>
+          <t>https://medicube.us/products/tatis-exclusive-all-about-glow-set?variant=41738370973744</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>[Subscr.] Collagen Glow Booster Milk Serum</t>
+          <t>[Tati's Exclusive] Plump Perfection Set</t>
         </is>
       </c>
       <c r="B251" t="inlineStr"/>
       <c r="C251" t="n">
-        <v>26</v>
+        <v>570</v>
+      </c>
+      <c r="D251" t="n">
+        <v>600.96</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr"/>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>PMEUS61012R00</t>
+          <t>KUSMEA00862</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/subscr-collagen-glow-booster-milk-serum</t>
+          <t>https://medicube.us/products/tatis-exclusive-plump-perfection-set</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>[Subscr.] Collagen Milky Glow Daytime Wrapping Mask</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr"/>
+          <t>[Tati's Exclusive] Ultimate At-Home Spa Essentials</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
       <c r="C252" t="n">
-        <v>24</v>
+        <v>855</v>
+      </c>
+      <c r="D252" t="n">
+        <v>1027</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="F252" t="inlineStr"/>
       <c r="G252" t="inlineStr">
         <is>
-          <t>PMEUS61005A01</t>
+          <t>KUSMEA00840</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/subscr-collagen-milky-glow-daytime-wrapping-mask</t>
+          <t>https://medicube.us/products/tatis-exclusive-ultimate-at-home-spa-essentials?variant=41738371891248</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>[Subscr.] Collagen Niacinamide Jelly Cream</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr"/>
+          <t>[Tati's Exclusive] Ultimate At-Home Spa Essentials</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Pink</t>
+        </is>
+      </c>
       <c r="C253" t="n">
-        <v>34</v>
+        <v>855</v>
+      </c>
+      <c r="D253" t="n">
+        <v>1027</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr">
         <is>
-          <t>PMEUS10003A00</t>
+          <t>KUSMEA00795</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/subscr-collagen-niacinamide-jelly-cream</t>
+          <t>https://medicube.us/products/tatis-exclusive-ultimate-at-home-spa-essentials?variant=41738371858480</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>[Subscr.] Collagen Night Wrapping Mask</t>
+          <t>[US ONLY] Collagen Glow Bubble Serum</t>
         </is>
       </c>
       <c r="B254" t="inlineStr"/>
       <c r="C254" t="n">
         <v>24</v>
       </c>
+      <c r="D254" t="n">
+        <v>26</v>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -15133,1561 +15238,10 @@
       <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr">
         <is>
-          <t>PMEUS10001A00</t>
+          <t>PMEUS61003A01</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-collagen-night-wrapping-mask</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>[Subscr.] Deep Reviving Bakuchiol Retinol Serum</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr"/>
-      <c r="C255" t="n">
-        <v>30</v>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr"/>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>PMEUS54011A00</t>
-        </is>
-      </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-deep-reviving-bakuchiol-retinol-serum</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>[Subscr.] Deep Vita C Capsule Cream</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr"/>
-      <c r="C256" t="n">
-        <v>34</v>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr"/>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>PMEUS10004A00</t>
-        </is>
-      </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-deep-vita-c-capsule-cream</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>[Subscr.] Deep Vita C Daily Quick Masks</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr"/>
-      <c r="C257" t="n">
-        <v>35</v>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr"/>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>PMEKR02045</t>
-        </is>
-      </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-deep-vita-c-daily-quick-masks</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>[Subscr.] Deep Vita C Pads</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr"/>
-      <c r="C258" t="n">
-        <v>35</v>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr"/>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>PMEUS10009A00</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-deep-vita-c-pads</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>[Subscr.] Hyaluronic Acid Capsule Cream</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr"/>
-      <c r="C259" t="n">
-        <v>34</v>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr"/>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>PMEUS43011R00</t>
-        </is>
-      </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-hyaluronic-acid-capsule-cream</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>[Subscr.] Hyaluronic Ceramide Moisturizing Jelly Cream</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr"/>
-      <c r="C260" t="n">
-        <v>17</v>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr"/>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>PMEUS43009R00</t>
-        </is>
-      </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-hyaluronic-ceramide-moisturizing-jelly-cream</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>[Subscr.] Hyaluronic Multi Peptide PDRN Serum</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr"/>
-      <c r="C261" t="n">
-        <v>26</v>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr"/>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>PMEKR43003R00</t>
-        </is>
-      </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-hyaluronic-multi-peptide-pdrn-serum</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>[Subscr.] Hypochlorous Acid Power Soothing Spray</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr"/>
-      <c r="C262" t="n">
-        <v>27</v>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr"/>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>PMEUS72006A00</t>
-        </is>
-      </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-hypochlorous-acid-power-soothing-spray</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>[Subscr.] Kojic Acid Turmeric Capsule Serum</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr"/>
-      <c r="C263" t="n">
-        <v>26</v>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F263" t="inlineStr"/>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>PMEUS68004A00</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-kojic-acid-turmeric-capsule-serum</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>[Subscr.] Kojic Acid Turmeric Gold Jelly Gel Mask</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>4EA</t>
-        </is>
-      </c>
-      <c r="C264" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F264" t="inlineStr"/>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>KUSMEA1429</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-kojic-acid-turmeric-gold-jelly-gel-mask</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>[Subscr.] Kojic Acid Turmeric Overnight Wrapping Mask</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr"/>
-      <c r="C265" t="n">
-        <v>24</v>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F265" t="inlineStr"/>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>PMEUS68001T00</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-kojic-acid-turmeric-overnight-wrapping-mask</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>[Subscr.] Kojic Acid Turmeric Toner</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr"/>
-      <c r="C266" t="n">
-        <v>27</v>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F266" t="inlineStr"/>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>PMEUS68003A00</t>
-        </is>
-      </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-kojic-acid-turmeric-toner</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>[Subscr.] Kojic Acid Turmeric Toner Pad</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr"/>
-      <c r="C267" t="n">
-        <v>31</v>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F267" t="inlineStr"/>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>PMEUS68005A01</t>
-        </is>
-      </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-kojic-acid-tumeric-toner-pad</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>[Subscr.] No Cast Just Glow Collagen Sunscreen</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr"/>
-      <c r="C268" t="n">
-        <v>22</v>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr"/>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>PMEKR61011R01</t>
-        </is>
-      </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-no-cast-just-glow-collagen-sunscreen</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>[Subscr.] PDRN Pink Caffeine Overnight Wrapping Mask</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr"/>
-      <c r="C269" t="n">
-        <v>24</v>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F269" t="inlineStr"/>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>PMEUS53019A00</t>
-        </is>
-      </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-pdrn-pink-caffeine-overnight-wrapping-mask</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>[Subscr.] PDRN Pink Collagen Bubble Serum</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr"/>
-      <c r="C270" t="n">
-        <v>26</v>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F270" t="inlineStr"/>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>PMEKR53022R00</t>
-        </is>
-      </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-pdrn-pink-collagen-bubble-serum</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>[Subscr.] PDRN Pink Collagen Capsule Cream</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr"/>
-      <c r="C271" t="n">
-        <v>34</v>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr"/>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>PMEUS53052R00</t>
-        </is>
-      </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-pdrn-pink-collagen-capsule-cream</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>[Subscr.] PDRN Pink Collagen Exosome Shot</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>MILD(2000)</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>24</v>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F272" t="inlineStr"/>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>PMEUS53006A00</t>
-        </is>
-      </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-pdrn-pink-collagen-exosome-shot?variant=42684285288496</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>[Subscr.] PDRN Pink Collagen Exosome Shot</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>STRONG(7500)</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>26</v>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F273" t="inlineStr"/>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>PMEUS53007A00</t>
-        </is>
-      </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-pdrn-pink-collagen-exosome-shot?variant=42684285321264</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>[Subscr.] PDRN Pink Collagen Gel Toner Pad</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr"/>
-      <c r="C274" t="n">
-        <v>33</v>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F274" t="inlineStr"/>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>PMEUS53012A01</t>
-        </is>
-      </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-pdrn-pink-collagen-gel-toner-pad</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>[Subscr.] PDRN Pink Gel Cleanser</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr"/>
-      <c r="C275" t="n">
-        <v>26</v>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F275" t="inlineStr"/>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>PMEUS53017A01</t>
-        </is>
-      </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-pdrn-pink-gel-cleanser</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>[Subscr.] PDRN Pink Niacinamide Milky Toner</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr"/>
-      <c r="C276" t="n">
-        <v>21</v>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F276" t="inlineStr"/>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>PMEUS53003A00</t>
-        </is>
-      </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-pdrn-pink-niacinamide-milky-toner</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>[Subscr.] PDRN Pink One Day Serum</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr"/>
-      <c r="C277" t="n">
-        <v>22</v>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F277" t="inlineStr"/>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>PMEUS53005A01</t>
-        </is>
-      </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-pdrn-pink-one-day-serum</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>[Subscr.] PDRN Pink Peptide Cream</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>Rose PDRN (Vegan)</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>27</v>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F278" t="inlineStr"/>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>PMEUS53003R00</t>
-        </is>
-      </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-pdrn-pink-peptide-cream?variant=42684285255728</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>[Subscr.] PDRN Pink Peptide Cream</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>Salmon DNA PDRN</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>27</v>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F279" t="inlineStr"/>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>PMEUS53002A00</t>
-        </is>
-      </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-pdrn-pink-peptide-cream?variant=42684285222960</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>[Subscr.] PDRN Pink Peptide Eye Cream</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr"/>
-      <c r="C280" t="n">
-        <v>28</v>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F280" t="inlineStr"/>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>PMEKR53014R00</t>
-        </is>
-      </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-pdrn-pink-peptide-eye-cream</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>[Subscr.] PDRN Pink Peptide Serum</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>Rose PDRN(Vegan)</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>28</v>
-      </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F281" t="inlineStr"/>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>PMEUS53001R00</t>
-        </is>
-      </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-pdrn-pink-peptide-serum?variant=42684282372144</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>[Subscr.] PDRN Pink Peptide Serum</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>Salmon DNA PDRN</t>
-        </is>
-      </c>
-      <c r="C282" t="n">
-        <v>28</v>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr"/>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>PMEUS53015A01</t>
-        </is>
-      </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-pdrn-pink-peptide-serum?variant=42684282339376</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>[Subscr.] PDRN Pink Peptide Toner</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>Rose</t>
-        </is>
-      </c>
-      <c r="C283" t="n">
-        <v>21</v>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>Esgotado</t>
-        </is>
-      </c>
-      <c r="F283" t="inlineStr"/>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>PMEUS53002R00</t>
-        </is>
-      </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-pdrn-pink-peptide-toner?variant=42684284928048</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>[Subscr.] PDRN Pink Peptide Toner</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>Salmon</t>
-        </is>
-      </c>
-      <c r="C284" t="n">
-        <v>21</v>
-      </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F284" t="inlineStr"/>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>PMEUS53008A01</t>
-        </is>
-      </c>
-      <c r="H284" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-pdrn-pink-peptide-toner?variant=42684284960816</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>[Subscr.] PDRN Pink Vita Coating Sheet Mask</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr"/>
-      <c r="C285" t="n">
-        <v>30</v>
-      </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F285" t="inlineStr"/>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>KUSMEA0201</t>
-        </is>
-      </c>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-pdrn-pink-vita-coating-sheet-mask</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>[Subscr.] Red Body Peeling Shot Cleanser</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr"/>
-      <c r="C286" t="n">
-        <v>24</v>
-      </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F286" t="inlineStr"/>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>PMEUS03009</t>
-        </is>
-      </c>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-red-body-peeling-shot-cleanser</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>[Subscr.] Red Clear Capsule Body Lotion</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr"/>
-      <c r="C287" t="n">
-        <v>23</v>
-      </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F287" t="inlineStr"/>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>PMEUS55022R00</t>
-        </is>
-      </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-red-clear-capsule-body-lotion</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>[Subscr.] Red Foam Cleanser</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr"/>
-      <c r="C288" t="n">
-        <v>23</v>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F288" t="inlineStr"/>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>PMEUS55002A00</t>
-        </is>
-      </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-red-foam-cleanser</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>[Subscr.] Red Succinic Acid Panthenol Pads</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr"/>
-      <c r="C289" t="n">
-        <v>26</v>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F289" t="inlineStr"/>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>PMEUS55004A01</t>
-        </is>
-      </c>
-      <c r="H289" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-red-succinic-acid-panthenol-pads</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>[Subscr.] Retinol NMN Boosting Serum</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr"/>
-      <c r="C290" t="n">
-        <v>26</v>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr"/>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>PMEKR43005R00</t>
-        </is>
-      </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-retinol-nmn-boosting-serum</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>[Subscr.] Salmon PDRN Pink Collagen Jelly Gel Mask</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr"/>
-      <c r="C291" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F291" t="inlineStr"/>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>KUSMEA1540</t>
-        </is>
-      </c>
-      <c r="H291" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-salmon-pdrn-pink-collagen-jelly-gel-mask</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>[Subscr.] TXA Niacinamide Capsule Cream</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr"/>
-      <c r="C292" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="D292" t="n">
-        <v>34</v>
-      </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F292" t="inlineStr"/>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>PMEUS43006A01</t>
-        </is>
-      </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-txa-niacinamide-capsule-cream</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>[Subscr.] TXA Niacinamide Serum</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr"/>
-      <c r="C293" t="n">
-        <v>26</v>
-      </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F293" t="inlineStr"/>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>PMEUS43002A01</t>
-        </is>
-      </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-txa-niacinamide-serum</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>[Subscr.] Triple Collagen Cream</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr"/>
-      <c r="C294" t="n">
-        <v>34</v>
-      </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr"/>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>PMEUS61010A01</t>
-        </is>
-      </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-triple-collagen-cream</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>[Subscr.] Zero Exosome Shot</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>MILD(2000)</t>
-        </is>
-      </c>
-      <c r="C295" t="n">
-        <v>24</v>
-      </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F295" t="inlineStr"/>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>PMEKR60006R02</t>
-        </is>
-      </c>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-zero-exosome-shot?variant=41281366163504</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>[Subscr.] Zero Exosome Shot</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>STRONG(7500)</t>
-        </is>
-      </c>
-      <c r="C296" t="n">
-        <v>26</v>
-      </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr"/>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>PMEUS10008R01</t>
-        </is>
-      </c>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-zero-exosome-shot?variant=41281366196272</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>[Subscr.] Zero Foam Cleanser</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr"/>
-      <c r="C297" t="n">
-        <v>22</v>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F297" t="inlineStr"/>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>PMEUS60004A01</t>
-        </is>
-      </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-zero-foam-cleanser</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>[Subscr.] Zero Pore Blackhead Deep Cleansing Oil</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr"/>
-      <c r="C298" t="n">
-        <v>27</v>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F298" t="inlineStr"/>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>PMEUS60020R01</t>
-        </is>
-      </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-zero-pore-blackhead-deep-cleansing-oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>[Subscr.] Zero Pore Blackhead Mud Mask</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr"/>
-      <c r="C299" t="n">
-        <v>20</v>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F299" t="inlineStr"/>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>PMEUS60018R00</t>
-        </is>
-      </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-zero-pore-blackhead-mud-mask</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>[Subscr.] Zero Pore Madecassoside Pads (Mild)</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr"/>
-      <c r="C300" t="n">
-        <v>31</v>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F300" t="inlineStr"/>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>PMEUS60003A00</t>
-        </is>
-      </c>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-zero-pore-pads-mild</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>[Subscr.] Zero Pore One-day Peptide Serum</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr"/>
-      <c r="C301" t="n">
-        <v>26</v>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F301" t="inlineStr"/>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>PMEUS60019R00</t>
-        </is>
-      </c>
-      <c r="H301" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-zero-pore-one-day-serum</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>[Subscr.] Zero Pore Pads</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr"/>
-      <c r="C302" t="n">
-        <v>31</v>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F302" t="inlineStr"/>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>PMEUS10002A00</t>
-        </is>
-      </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/subscr-zero-pore-pads</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>[Tati's Exclusive] All About Glow Set</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>Collagen Wrapping Mask Set</t>
-        </is>
-      </c>
-      <c r="C303" t="n">
-        <v>540</v>
-      </c>
-      <c r="D303" t="n">
-        <v>575</v>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>Esgotado</t>
-        </is>
-      </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G303" t="inlineStr">
-        <is>
-          <t>KUSMEA00793</t>
-        </is>
-      </c>
-      <c r="H303" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/tatis-exclusive-all-about-glow-set?variant=41738371006512</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>[Tati's Exclusive] All About Glow Set</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>PDRN Gel Mask Set</t>
-        </is>
-      </c>
-      <c r="C304" t="n">
-        <v>540</v>
-      </c>
-      <c r="D304" t="n">
-        <v>574.96</v>
-      </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>Esgotado</t>
-        </is>
-      </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>KUSMEA00844</t>
-        </is>
-      </c>
-      <c r="H304" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/tatis-exclusive-all-about-glow-set?variant=41738370973744</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>[Tati's Exclusive] Plump Perfection Set</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr"/>
-      <c r="C305" t="n">
-        <v>570</v>
-      </c>
-      <c r="D305" t="n">
-        <v>600.96</v>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>Esgotado</t>
-        </is>
-      </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>KUSMEA00862</t>
-        </is>
-      </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/tatis-exclusive-plump-perfection-set</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>[Tati's Exclusive] Ultimate At-Home Spa Essentials</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="C306" t="n">
-        <v>855</v>
-      </c>
-      <c r="D306" t="n">
-        <v>1027</v>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>Esgotado</t>
-        </is>
-      </c>
-      <c r="F306" t="inlineStr"/>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>KUSMEA00840</t>
-        </is>
-      </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/tatis-exclusive-ultimate-at-home-spa-essentials?variant=41738371891248</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>[Tati's Exclusive] Ultimate At-Home Spa Essentials</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>Pink</t>
-        </is>
-      </c>
-      <c r="C307" t="n">
-        <v>855</v>
-      </c>
-      <c r="D307" t="n">
-        <v>1027</v>
-      </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>Esgotado</t>
-        </is>
-      </c>
-      <c r="F307" t="inlineStr"/>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>KUSMEA00795</t>
-        </is>
-      </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>https://medicube.us/products/tatis-exclusive-ultimate-at-home-spa-essentials?variant=41738371858480</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>[US ONLY] Collagen Glow Bubble Serum</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr"/>
-      <c r="C308" t="n">
-        <v>24</v>
-      </c>
-      <c r="D308" t="n">
-        <v>26</v>
-      </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F308" t="inlineStr"/>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>PMEUS61003A01</t>
-        </is>
-      </c>
-      <c r="H308" t="inlineStr">
         <is>
           <t>https://medicube.us/products/collagen-glow-bubble-serum</t>
         </is>
@@ -16948,60 +15502,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H252" r:id="rId251"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H253" r:id="rId252"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H254" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H255" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H256" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H257" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H260" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H261" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H262" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H266" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H267" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H268" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H269" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H271" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H272" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H273" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H274" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H275" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H276" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H277" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H278" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H279" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H280" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H281" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H282" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H283" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H284" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H285" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H286" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H287" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H288" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H289" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H290" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H293" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H294" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H295" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H296" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H297" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H298" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H299" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H302" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H303" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H304" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H305" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H306" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H307" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId307"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17049,7 +15549,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site oficial: https://medicube.us · loja "MEDICUBE US" · moeda USD · lido em 30/10/2026 06:02 UTC</t>
+          <t>Site oficial: https://medicube.us · loja "MEDICUBE US" · moeda USD · lido em 30/10/2026 06:04 UTC</t>
         </is>
       </c>
     </row>

--- a/tools/precos/planilhas/precos-oficiais-medicube.xlsx
+++ b/tools/precos/planilhas/precos-oficiais-medicube.xlsx
@@ -15549,7 +15549,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site oficial: https://medicube.us · loja "MEDICUBE US" · moeda USD · lido em 30/10/2026 06:04 UTC</t>
+          <t>Site oficial: https://medicube.us · loja "MEDICUBE US" · moeda USD · lido em 30/10/2026 06:05 UTC</t>
         </is>
       </c>
     </row>

--- a/tools/precos/planilhas/precos-oficiais-medicube.xlsx
+++ b/tools/precos/planilhas/precos-oficiais-medicube.xlsx
@@ -684,12 +684,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MB003292</t>
+          <t>MB003323</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Azelaic Acid 16 Calming Serum: sérum calmante com ácido azelaico e niacinamida</t>
+          <t>Affordable Glass Glow 7-Day Set: rotina de 5 passos com exossomos e colágeno</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>174.9</v>
+        <v>561.9</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -707,15 +707,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Azelaic Acid 16 Calming Serum</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Affordable Glass Glow 7-Day Skincare Set</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Collagen Jelly Cream</t>
+        </is>
+      </c>
       <c r="H4" s="4" t="n">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>26</v>
+        <v>155</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -724,7 +728,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/azelaic-acid-16-calming-serum</t>
+          <t>https://medicube.us/products/affordable-glass-glow-7-day-skincare-set?variant=41592205738032</t>
         </is>
       </c>
       <c r="L4" s="2">
@@ -739,12 +743,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MB003229</t>
+          <t>MB003292</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Azelaic Acid Capsule Foam Cleanser: espuma com cápsulas de ácido azelaico</t>
+          <t>Azelaic Acid 16 Calming Serum: sérum calmante com ácido azelaico e niacinamida</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -753,7 +757,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>145.9</v>
+        <v>174.9</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -762,15 +766,15 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Azelaic Acid Capsule Foam Cleanser</t>
+          <t>Azelaic Acid 16 Calming Serum</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -779,7 +783,7 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/azelaic-acid-capsule-foam-cleanser</t>
+          <t>https://medicube.us/products/azelaic-acid-16-calming-serum</t>
         </is>
       </c>
       <c r="L5" s="2">
@@ -794,12 +798,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MB003225</t>
+          <t>MB003229</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Azelaic Acid Exosome Shot: sérum com microespículas, ácido azelaico e exossomos</t>
+          <t>Azelaic Acid Capsule Foam Cleanser: espuma com cápsulas de ácido azelaico</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -808,7 +812,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>160.9</v>
+        <v>145.9</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -817,20 +821,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Azelaic Acid Exosome Shot</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>MILD(2000)</t>
-        </is>
-      </c>
+          <t>Azelaic Acid Capsule Foam Cleanser</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I6" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="I6" s="4" t="n">
-        <v>24</v>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -838,7 +838,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/azelaic-acid-exosome-shot?variant=43053899448368</t>
+          <t>https://medicube.us/products/azelaic-acid-capsule-foam-cleanser</t>
         </is>
       </c>
       <c r="L6" s="2">
@@ -853,12 +853,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MB003226</t>
+          <t>MB003225</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Azelaic Acid Niacinamide Clarifying Toner: tônico com 4% de ácido azelaico</t>
+          <t>Azelaic Acid Exosome Shot: sérum com microespículas, ácido azelaico e exossomos</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>153.9</v>
+        <v>160.9</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
@@ -876,14 +876,20 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Azelaic Acid Niacinamide Clarifying Toner</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Azelaic Acid Exosome Shot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MILD(2000)</t>
+        </is>
+      </c>
       <c r="H7" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="I7" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>24</v>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -891,7 +897,7 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/azelaic-acid-niacinamide-clarifying-toner</t>
+          <t>https://medicube.us/products/azelaic-acid-exosome-shot?variant=43053899448368</t>
         </is>
       </c>
       <c r="L7" s="2">
@@ -906,12 +912,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MB003303</t>
+          <t>MB003226</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Collagen Glow Booster Milk Serum: sérum leitoso com colágeno e niacinamida 110 ml</t>
+          <t>Azelaic Acid Niacinamide Clarifying Toner: tônico com 4% de ácido azelaico</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -920,7 +926,7 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>174.9</v>
+        <v>153.9</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
@@ -929,20 +935,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Collagen Glow Booster Milk Serum</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>SINGLE</t>
-        </is>
-      </c>
+          <t>Azelaic Acid Niacinamide Clarifying Toner</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>26</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I8" s="4" t="n"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -950,7 +950,7 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/collagen-glow-booster-milk-serum?variant=41350297649200</t>
+          <t>https://medicube.us/products/azelaic-acid-niacinamide-clarifying-toner</t>
         </is>
       </c>
       <c r="L8" s="2">
@@ -965,12 +965,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MB003305</t>
+          <t>MB003303</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Collagen Milky Glow Daytime Wrapping Mask: máscara peel-off de colágeno e leite</t>
+          <t>Collagen Glow Booster Milk Serum: sérum leitoso com colágeno e niacinamida 110 ml</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Collagen Milky Glow Daytime Wrapping Mask</t>
+          <t>Collagen Glow Booster Milk Serum</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -999,7 +999,9 @@
       <c r="H9" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="I9" s="4" t="n"/>
+      <c r="I9" s="4" t="n">
+        <v>26</v>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1007,7 +1009,7 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/collagen-milk-toning-wrapping-mask?variant=42501172199472</t>
+          <t>https://medicube.us/products/collagen-glow-booster-milk-serum?variant=41350297649200</t>
         </is>
       </c>
       <c r="L9" s="2">
@@ -1022,12 +1024,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MB003317</t>
+          <t>MB003304</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Collagen Niacinamide Jelly Cream: gel-creme de colágeno e niacinamida</t>
+          <t>Collagen Glow Bubble Serum: sérum em mousse com 11 tipos de colágeno 100 ml</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1036,7 +1038,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>104.9</v>
+        <v>174.9</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
@@ -1045,20 +1047,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Collagen Niacinamide Jelly Cream</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>110ml</t>
-        </is>
-      </c>
+          <t>[US ONLY] Collagen Glow Bubble Serum</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="I10" s="4" t="n">
-        <v>34</v>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1066,7 +1064,7 @@
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/collagen-niacinamide-jelly-cream?variant=40889653493808</t>
+          <t>https://medicube.us/products/collagen-glow-bubble-serum</t>
         </is>
       </c>
       <c r="L10" s="2">
@@ -1081,12 +1079,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MB003319</t>
+          <t>MB003305</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Collagen Swirl Duo: gel-creme de colágeno + creme de colágeno para misturar</t>
+          <t>Collagen Milky Glow Daytime Wrapping Mask: máscara peel-off de colágeno e leite</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1095,7 +1093,7 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>567.9</v>
+        <v>174.9</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
@@ -1104,16 +1102,18 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Collagen Swirl Duo</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>Collagen Milky Glow Daytime Wrapping Mask</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
       <c r="H11" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>78</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="I11" s="4" t="n"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/collagen-swirl-duo</t>
+          <t>https://medicube.us/products/collagen-milk-toning-wrapping-mask?variant=42501172199472</t>
         </is>
       </c>
       <c r="L11" s="2">
@@ -1136,12 +1136,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MB003278</t>
+          <t>MB003317</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deep Peptide Radiance Mask: máscara em folha com 4 peptídeos e ácido hialurônico</t>
+          <t>Collagen Niacinamide Jelly Cream: gel-creme de colágeno e niacinamida</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>42.9</v>
+        <v>104.9</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
@@ -1159,19 +1159,19 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Deep Peptide Radiance Mask</t>
+          <t>Collagen Niacinamide Jelly Cream</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2 MASKS</t>
+          <t>110ml</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/medicube-deep-peptide-radiance-mask-2ea?variant=40999586234416</t>
+          <t>https://medicube.us/products/collagen-niacinamide-jelly-cream?variant=40889653493808</t>
         </is>
       </c>
       <c r="L12" s="2">
@@ -1195,12 +1195,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MB003280</t>
+          <t>MB003319</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deep Reviving Bakuchiol Retinol Serum: sérum de retinol e bakuchiol 30 ml</t>
+          <t>Collagen Swirl Duo: gel-creme de colágeno + creme de colágeno para misturar</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>174.9</v>
+        <v>567.9</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
@@ -1218,19 +1218,15 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Deep Reviving Bakuchiol Retinol Serum</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SINGLE</t>
-        </is>
-      </c>
+          <t>Collagen Swirl Duo</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" s="4" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1239,7 +1235,7 @@
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/deep-reviving-bakuchiol-retinol-serum?variant=41189259542576</t>
+          <t>https://medicube.us/products/collagen-swirl-duo</t>
         </is>
       </c>
       <c r="L13" s="2">
@@ -1254,12 +1250,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MB003250</t>
+          <t>MB003278</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deep Reviving Peptide Eye Cream: creme para a área dos olhos com peptídeos 30 ml</t>
+          <t>Deep Peptide Radiance Mask: máscara em folha com 4 peptídeos e ácido hialurônico</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1268,7 +1264,7 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>188.9</v>
+        <v>42.9</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
@@ -1277,15 +1273,19 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Deep Reviving Peptide Eye Cream</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>Deep Peptide Radiance Mask</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2 MASKS</t>
+        </is>
+      </c>
       <c r="H14" s="4" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/deep-reviving-peptide-eye-cream-1</t>
+          <t>https://medicube.us/products/medicube-deep-peptide-radiance-mask-2ea?variant=40999586234416</t>
         </is>
       </c>
       <c r="L14" s="2">
@@ -1309,12 +1309,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MB003244</t>
+          <t>MB003280</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deep Vita C Daily Quick Masks: 30 máscaras de 1 minuto com vitaminas</t>
+          <t>Deep Reviving Bakuchiol Retinol Serum: sérum de retinol e bakuchiol 30 ml</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>254.9</v>
+        <v>174.9</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -1332,15 +1332,19 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Deep Vita C Daily Quick Masks</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Deep Reviving Bakuchiol Retinol Serum</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
       <c r="H15" s="4" t="n">
         <v>24</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1349,7 +1353,7 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/deep-vita-c-daily-quick-masks</t>
+          <t>https://medicube.us/products/deep-reviving-bakuchiol-retinol-serum?variant=41189259542576</t>
         </is>
       </c>
       <c r="L15" s="2">
@@ -1364,12 +1368,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MB003281</t>
+          <t>MB003250</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deep Vita C Pads: discos de vitamina C para tom uniforme (70 discos)</t>
+          <t>Deep Reviving Peptide Eye Cream: creme para a área dos olhos com peptídeos 30 ml</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1378,7 +1382,7 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>169.9</v>
+        <v>188.9</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -1387,19 +1391,15 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Deep Vita C Pads</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SINGLE</t>
-        </is>
-      </c>
+          <t>Deep Reviving Peptide Eye Cream</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/deep-vita-c-pad?variant=40708793172016</t>
+          <t>https://medicube.us/products/deep-reviving-peptide-eye-cream-1</t>
         </is>
       </c>
       <c r="L16" s="2">
@@ -1423,12 +1423,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MB003237</t>
+          <t>MB003244</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Deep Vitamin C Capsule Serum: sérum de vitamina C em cápsulas com niacinamida</t>
+          <t>Deep Vita C Daily Quick Masks: 30 máscaras de 1 minuto com vitaminas</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>174.9</v>
+        <v>254.9</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deep Vitamin C Capsule Serum</t>
+          <t>Deep Vita C Daily Quick Masks</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1454,7 +1454,7 @@
         <v>24</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/deep-vitamin-c-capsule-serum</t>
+          <t>https://medicube.us/products/deep-vita-c-daily-quick-masks</t>
         </is>
       </c>
       <c r="L17" s="2">
@@ -1478,12 +1478,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MB003257</t>
+          <t>MB003281</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Glass Glow Duo: tônico e sérum com três tipos de colágeno</t>
+          <t>Deep Vita C Pads: discos de vitamina C para tom uniforme (70 discos)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>480.9</v>
+        <v>169.9</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -1501,15 +1501,19 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Glass Glow Duo</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>Deep Vita C Pads</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
       <c r="H18" s="4" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1518,7 +1522,7 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/triple-collagen-set</t>
+          <t>https://medicube.us/products/deep-vita-c-pad?variant=40708793172016</t>
         </is>
       </c>
       <c r="L18" s="2">
@@ -1533,12 +1537,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MB003318</t>
+          <t>MB003237</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Glazed Milk Duo: sérum leitoso de colágeno + máscara noturna peel-off</t>
+          <t>Deep Vitamin C Capsule Serum: sérum de vitamina C em cápsulas com niacinamida</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1547,7 +1551,7 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>328.9</v>
+        <v>174.9</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
@@ -1556,15 +1560,15 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Glazed Milk Duo</t>
+          <t>Deep Vitamin C Capsule Serum</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" s="4" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1573,7 +1577,7 @@
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/glazed-milk-duo</t>
+          <t>https://medicube.us/products/deep-vitamin-c-capsule-serum</t>
         </is>
       </c>
       <c r="L19" s="2">
@@ -1588,12 +1592,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MB003300</t>
+          <t>MB003257</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hyaluronic Acid Capsule Cream: creme com cápsulas de ácido hialurônico 55 g</t>
+          <t>Glass Glow Duo: tônico e sérum com três tipos de colágeno</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,7 +1606,7 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>169.9</v>
+        <v>480.9</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -1611,19 +1615,15 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hyaluronic Acid Capsule Cream</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>SINGLE</t>
-        </is>
-      </c>
+          <t>Glass Glow Duo</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" s="4" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/hyaluronic-acid-capsule-cream?variant=42525945167920</t>
+          <t>https://medicube.us/products/triple-collagen-set</t>
         </is>
       </c>
       <c r="L20" s="2">
@@ -1647,12 +1647,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MB003268</t>
+          <t>MB003318</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hyaluronic Ceramide Moisturizing Jelly Cream: gel-creme com ácido hialurônico</t>
+          <t>Glazed Milk Duo: sérum leitoso de colágeno + máscara noturna peel-off</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>189.9</v>
+        <v>328.9</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
@@ -1670,14 +1670,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hyaluronic Ceramide Moisturizing Jelly Cream</t>
+          <t>Glazed Milk Duo</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="I21" s="4" t="n"/>
+        <v>45</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>52</v>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1685,7 +1687,7 @@
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/hyaluronic-ceramide-moisturizing-jelly-cream</t>
+          <t>https://medicube.us/products/glazed-milk-duo</t>
         </is>
       </c>
       <c r="L21" s="2">
@@ -1700,12 +1702,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MB003267</t>
+          <t>MB003300</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hyaluronic Multi Peptide PDRN Serum: sérum bifásico com ácido hialurônico e PDRN</t>
+          <t>Hyaluronic Acid Capsule Cream: creme com cápsulas de ácido hialurônico 55 g</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1714,7 +1716,7 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>145.9</v>
+        <v>169.9</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -1723,15 +1725,19 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hyaluronic Multi Peptide PDRN Serum</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>Hyaluronic Acid Capsule Cream</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
       <c r="H22" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1740,7 +1746,7 @@
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/hyaluronic-multi-peptide-pdrn-serum</t>
+          <t>https://medicube.us/products/hyaluronic-acid-capsule-cream?variant=42525945167920</t>
         </is>
       </c>
       <c r="L22" s="2">
@@ -1755,12 +1761,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MB003228</t>
+          <t>MB003268</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hypochlorous Acid Peel Mask: máscara em folha peel-off para cravos e poros</t>
+          <t>Hyaluronic Ceramide Moisturizing Jelly Cream: gel-creme com ácido hialurônico</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1778,16 +1784,14 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hypochlorous Acid Peel Mask</t>
+          <t>Hyaluronic Ceramide Moisturizing Jelly Cream</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>28</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I23" s="4" t="n"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1795,7 +1799,7 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/hypochlorous-acid-peel-mask</t>
+          <t>https://medicube.us/products/hyaluronic-ceramide-moisturizing-jelly-cream</t>
         </is>
       </c>
       <c r="L23" s="2">
@@ -1810,12 +1814,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MB003331</t>
+          <t>MB003267</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hypochlorous Acid Power Soothing Spray: spray calmante com ácido hipocloroso</t>
+          <t>Hyaluronic Multi Peptide PDRN Serum: sérum bifásico com ácido hialurônico e PDRN</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1824,7 +1828,7 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>159.9</v>
+        <v>145.9</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -1833,15 +1837,15 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hypochlorous Acid Power Soothing Spray</t>
+          <t>Hyaluronic Multi Peptide PDRN Serum</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1850,7 +1854,7 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/hypochlorous-acid-power-soothing-spray</t>
+          <t>https://medicube.us/products/hyaluronic-multi-peptide-pdrn-serum</t>
         </is>
       </c>
       <c r="L24" s="2">
@@ -1865,12 +1869,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MB003241</t>
+          <t>MB003228</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hypochlorous Acid Rice Body Peel Shot: esfoliante corporal com ácido hipocloroso</t>
+          <t>Hypochlorous Acid Peel Mask: máscara em folha peel-off para cravos e poros</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1879,7 +1883,7 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>204.9</v>
+        <v>189.9</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
@@ -1888,14 +1892,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hypochlorous Acid Rice Body Peel Shot</t>
+          <t>Hypochlorous Acid Peel Mask</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="I25" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="I25" s="4" t="n"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1903,7 +1909,7 @@
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/hypochlorous-acid-rice-body-peel-shot</t>
+          <t>https://medicube.us/products/hypochlorous-acid-peel-mask</t>
         </is>
       </c>
       <c r="L25" s="2">
@@ -1918,12 +1924,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MB003235</t>
+          <t>MB003331</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Body Peel Shot: esfoliante corporal com ácido kójico e cúrcuma</t>
+          <t>Hypochlorous Acid Power Soothing Spray: spray calmante com ácido hipocloroso</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1932,7 +1938,7 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>203.9</v>
+        <v>159.9</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -1941,14 +1947,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Body Peel Shot</t>
+          <t>Hypochlorous Acid Power Soothing Spray</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="I26" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>27</v>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1956,7 +1964,7 @@
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/kojic-acid-turmeric-body-peel-shot</t>
+          <t>https://medicube.us/products/hypochlorous-acid-power-soothing-spray</t>
         </is>
       </c>
       <c r="L26" s="2">
@@ -1971,12 +1979,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MB003243</t>
+          <t>MB003241</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Brightening Body Wash: sabonete líquido corporal iluminador</t>
+          <t>Hypochlorous Acid Rice Body Peel Shot: esfoliante corporal com ácido hipocloroso</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1985,7 +1993,7 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>160.9</v>
+        <v>204.9</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
@@ -1994,20 +2002,14 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Brightening Body Wash</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>400ml</t>
-        </is>
-      </c>
+          <t>Hypochlorous Acid Rice Body Peel Shot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>24</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="I27" s="4" t="n"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2015,7 +2017,7 @@
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/kojic-acid-turmeric-brightening-body-wash?variant=43582251532336</t>
+          <t>https://medicube.us/products/hypochlorous-acid-rice-body-peel-shot</t>
         </is>
       </c>
       <c r="L27" s="2">
@@ -2030,12 +2032,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MB003298</t>
+          <t>MB003235</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Capsule Serum: sérum em cápsulas com ácido kójico e cúrcuma</t>
+          <t>Kojic Acid Turmeric Body Peel Shot: esfoliante corporal com ácido kójico e cúrcuma</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2044,7 +2046,7 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>189.9</v>
+        <v>203.9</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -2053,16 +2055,14 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Capsule Serum</t>
+          <t>Kojic Acid Turmeric Body Peel Shot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>26</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="I28" s="4" t="n"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/kojic-acid-turmeric-capsule-serum</t>
+          <t>https://medicube.us/products/kojic-acid-turmeric-body-peel-shot</t>
         </is>
       </c>
       <c r="L28" s="2">
@@ -2085,12 +2085,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MB003238</t>
+          <t>MB003243</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Eye Gel Serum: gel para a área dos olhos com ácido kójico e cafeína</t>
+          <t>Kojic Acid Turmeric Brightening Body Wash: sabonete líquido corporal iluminador</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>203.9</v>
+        <v>160.9</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
@@ -2108,15 +2108,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Eye Gel Serum</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>Kojic Acid Turmeric Brightening Body Wash</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>400ml</t>
+        </is>
+      </c>
       <c r="H29" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2125,7 +2129,7 @@
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/kojic-acid-tumeric-eye-gel-serum</t>
+          <t>https://medicube.us/products/kojic-acid-turmeric-brightening-body-wash?variant=43582251532336</t>
         </is>
       </c>
       <c r="L29" s="2">
@@ -2140,12 +2144,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MB003295</t>
+          <t>MB003298</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Gold Jelly Gel Mask: máscara de gel dourada com ácido kójico</t>
+          <t>Kojic Acid Turmeric Capsule Serum: sérum em cápsulas com ácido kójico e cúrcuma</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2154,7 +2158,7 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>175.9</v>
+        <v>189.9</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
@@ -2163,19 +2167,15 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Gold Jelly Gel Mask</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>1EA</t>
-        </is>
-      </c>
+          <t>Kojic Acid Turmeric Capsule Serum</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" s="4" t="n">
-        <v>5.99</v>
+        <v>24</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>6.99</v>
+        <v>26</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/kojic-acid-turmeric-gold-jelly-gel-mask?variant=41785703465008</t>
+          <t>https://medicube.us/products/kojic-acid-turmeric-capsule-serum</t>
         </is>
       </c>
       <c r="L30" s="2">
@@ -2199,12 +2199,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MB003297</t>
+          <t>MB003238</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Toner Pad: discos com ácido kójico e cúrcuma (70 discos)</t>
+          <t>Kojic Acid Turmeric Eye Gel Serum: gel para a área dos olhos com ácido kójico e cafeína</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>225.9</v>
+        <v>203.9</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
@@ -2222,15 +2222,15 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Toner Pad</t>
+          <t>Kojic Acid Turmeric Eye Gel Serum</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/kojic-acid-tumeric-toner-pad</t>
+          <t>https://medicube.us/products/kojic-acid-tumeric-eye-gel-serum</t>
         </is>
       </c>
       <c r="L31" s="2">
@@ -2254,12 +2254,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MB003240</t>
+          <t>MB003295</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Vita Capsule Cream: creme em cápsulas com ácido kójico e cúrcuma</t>
+          <t>Kojic Acid Turmeric Gold Jelly Gel Mask: máscara de gel dourada com ácido kójico</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>189.9</v>
+        <v>175.9</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -2277,15 +2277,19 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Vita Capsule Cream</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>Kojic Acid Turmeric Gold Jelly Gel Mask</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1EA</t>
+        </is>
+      </c>
       <c r="H32" s="4" t="n">
-        <v>26</v>
+        <v>5.99</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>34</v>
+        <v>6.99</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2294,7 +2298,7 @@
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/kojic-acid-turmeric-vita-capsule-cream</t>
+          <t>https://medicube.us/products/kojic-acid-turmeric-gold-jelly-gel-mask?variant=41785703465008</t>
         </is>
       </c>
       <c r="L32" s="2">
@@ -2309,12 +2313,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MB003231</t>
+          <t>MB003297</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Vita Capsule Foam Cleanser: espuma com ácido kójico e cúrcuma</t>
+          <t>Kojic Acid Turmeric Toner Pad: discos com ácido kójico e cúrcuma (70 discos)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2323,7 +2327,7 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>145.9</v>
+        <v>225.9</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
@@ -2332,15 +2336,15 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Vita Capsule Foam Cleanser</t>
+          <t>Kojic Acid Turmeric Toner Pad</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2349,7 +2353,7 @@
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/kojic-acid-turmeric-vita-capsule-foam-cleanser</t>
+          <t>https://medicube.us/products/kojic-acid-tumeric-toner-pad</t>
         </is>
       </c>
       <c r="L33" s="2">
@@ -2364,12 +2368,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MB003324</t>
+          <t>MB003240</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Vitamin Gold Jelly Mist Serum: sérum em spray iluminador</t>
+          <t>Kojic Acid Turmeric Vita Capsule Cream: creme em cápsulas com ácido kójico e cúrcuma</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2378,7 +2382,7 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>160.9</v>
+        <v>189.9</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
@@ -2387,19 +2391,15 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Vitamin Gold Jelly Mist Serum</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>100ml</t>
-        </is>
-      </c>
+          <t>Kojic Acid Turmeric Vita Capsule Cream</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/turmeric-vitamin-gold-jelly-mist-serum?variant=43624986148912</t>
+          <t>https://medicube.us/products/kojic-acid-turmeric-vita-capsule-cream</t>
         </is>
       </c>
       <c r="L34" s="2">
@@ -2423,12 +2423,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MB003332</t>
+          <t>MB003231</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>No Cast Just Glow Collagen Sunscreen: protetor solar com colágeno FPS 50</t>
+          <t>Kojic Acid Turmeric Vita Capsule Foam Cleanser: espuma com ácido kójico e cúrcuma</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>159.9</v>
+        <v>145.9</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
@@ -2446,14 +2446,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>No Cast Just Glow Collagen Sunscreen</t>
+          <t>Kojic Acid Turmeric Vita Capsule Foam Cleanser</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I35" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="I35" s="4" t="n"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2461,7 +2463,7 @@
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/no-cast-just-glow-collagen-sunscreen</t>
+          <t>https://medicube.us/products/kojic-acid-turmeric-vita-capsule-foam-cleanser</t>
         </is>
       </c>
       <c r="L35" s="2">
@@ -2476,12 +2478,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MB003310</t>
+          <t>MB003324</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PDRN Lip Sleeping Mask: máscara noturna para os lábios com PDRN e karité</t>
+          <t>Kojic Acid Turmeric Vitamin Gold Jelly Mist Serum: sérum em spray iluminador</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2490,7 +2492,7 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>137.9</v>
+        <v>160.9</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
@@ -2499,15 +2501,19 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PDRN Lip Sleeping Mask</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>Kojic Acid Turmeric Vitamin Gold Jelly Mist Serum</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
       <c r="H36" s="4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2516,7 +2522,7 @@
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-lip-sleeping-mask</t>
+          <t>https://medicube.us/products/turmeric-vitamin-gold-jelly-mist-serum?variant=43624986148912</t>
         </is>
       </c>
       <c r="L36" s="2">
@@ -2531,12 +2537,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MB003309</t>
+          <t>MB003332</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PDRN Pink Caffeine Overnight Wrapping Mask: máscara noturna peel-off com PDRN</t>
+          <t>No Cast Just Glow Collagen Sunscreen: protetor solar com colágeno FPS 50</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2545,7 +2551,7 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>127.9</v>
+        <v>159.9</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
@@ -2554,16 +2560,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PDRN Pink Caffeine Overnight Wrapping Mask</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
+          <t>No Cast Just Glow Collagen Sunscreen</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I37" s="4" t="n"/>
       <c r="J37" t="inlineStr">
@@ -2573,7 +2575,7 @@
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-wrapping-mask?variant=42200876679216</t>
+          <t>https://medicube.us/products/no-cast-just-glow-collagen-sunscreen</t>
         </is>
       </c>
       <c r="L37" s="2">
@@ -2588,12 +2590,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MB003329</t>
+          <t>MB003310</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PDRN Pink Collagen Exosome Shot: sérum com microespículas, PDRN e exossomos</t>
+          <t>PDRN Lip Sleeping Mask: máscara noturna para os lábios com PDRN e karité</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2602,7 +2604,7 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>140.9</v>
+        <v>137.9</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
@@ -2611,19 +2613,15 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PDRN Pink Collagen Exosome Shot</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>MILD(2000)</t>
-        </is>
-      </c>
+          <t>PDRN Lip Sleeping Mask</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2632,7 +2630,7 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-pink-collagen-exosome-shot?variant=41877873328176</t>
+          <t>https://medicube.us/products/pdrn-lip-sleeping-mask</t>
         </is>
       </c>
       <c r="L38" s="2">
@@ -2647,12 +2645,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MB003307</t>
+          <t>MB003309</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PDRN Pink Collagen Gel Toner Pad: discos de gel com PDRN, colágeno e niacinamida</t>
+          <t>PDRN Pink Caffeine Overnight Wrapping Mask: máscara noturna peel-off com PDRN</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2661,7 +2659,7 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>151.9</v>
+        <v>127.9</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
@@ -2670,16 +2668,18 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PDRN Pink Collagen Gel Toner Pad</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>PDRN Pink Caffeine Overnight Wrapping Mask</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
       <c r="H39" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <v>33</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="I39" s="4" t="n"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-pink-collagen-gel-toner-pad</t>
+          <t>https://medicube.us/products/pdrn-wrapping-mask?variant=42200876679216</t>
         </is>
       </c>
       <c r="L39" s="2">
@@ -2702,12 +2702,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MB003314</t>
+          <t>MB003329</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PDRN Pink Gel Cleanser: gel de limpeza que vira espuma, com PDRN, colágeno e LHA</t>
+          <t>PDRN Pink Collagen Exosome Shot: sérum com microespículas, PDRN e exossomos</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>189.9</v>
+        <v>140.9</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
@@ -2725,14 +2725,20 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PDRN Pink Gel Cleanser</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>PDRN Pink Collagen Exosome Shot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>MILD(2000)</t>
+        </is>
+      </c>
       <c r="H40" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="I40" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>24</v>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2740,7 +2746,7 @@
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-gel-cleanser</t>
+          <t>https://medicube.us/products/pdrn-pink-collagen-exosome-shot?variant=41877873328176</t>
         </is>
       </c>
       <c r="L40" s="2">
@@ -2755,12 +2761,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MB003230</t>
+          <t>MB003307</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PDRN Pink Glutathione Capsule Foam Cleanser: espuma com PDRN e glutationa</t>
+          <t>PDRN Pink Collagen Gel Toner Pad: discos de gel com PDRN, colágeno e niacinamida</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2769,7 +2775,7 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>144.9</v>
+        <v>151.9</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
@@ -2778,15 +2784,15 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PDRN Pink Glutathione Capsule Foam Cleanser</t>
+          <t>PDRN Pink Collagen Gel Toner Pad</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2795,7 +2801,7 @@
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-pink-glutathione-capsule-foam-cleanser</t>
+          <t>https://medicube.us/products/pdrn-pink-collagen-gel-toner-pad</t>
         </is>
       </c>
       <c r="L41" s="2">
@@ -2810,12 +2816,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MB003308</t>
+          <t>MB003314</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PDRN Pink Niacinamide Milky Toner: tônico leitoso com PDRN, ceramida e peptídeos</t>
+          <t>PDRN Pink Gel Cleanser: gel de limpeza que vira espuma, com PDRN, colágeno e LHA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2824,7 +2830,7 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>121.9</v>
+        <v>189.9</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -2833,12 +2839,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PDRN Pink Niacinamide Milky Toner</t>
+          <t>PDRN Pink Gel Cleanser</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" s="4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I42" s="4" t="n"/>
       <c r="J42" t="inlineStr">
@@ -2848,7 +2854,7 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-pink-niacinamide-milky-toner</t>
+          <t>https://medicube.us/products/pdrn-gel-cleanser</t>
         </is>
       </c>
       <c r="L42" s="2">
@@ -2863,12 +2869,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MB003327</t>
+          <t>MB003316</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PDRN Pink One Day Serum: ampola de dose única com PDRN, colágeno e glutationa</t>
+          <t>PDRN Pink Glow Full Set: tônico, sérum e creme com PDRN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2877,7 +2883,7 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>137.9</v>
+        <v>655.9</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
@@ -2886,24 +2892,28 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PDRN Pink One Day Serum</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>PDRN Pink Glow Full Set</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Rose PDRN (Vegan)</t>
+        </is>
+      </c>
       <c r="H43" s="4" t="n">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>22</v>
+        <v>95.98</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-pink-one-day-serum</t>
+          <t>https://medicube.us/products/pdrn-exosome-set?variant=41729848508464</t>
         </is>
       </c>
       <c r="L43" s="2">
@@ -2918,12 +2928,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MB003313</t>
+          <t>MB003230</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PDRN Pink Peptide Eye Cream: creme para a área dos olhos com PDRN e retinol</t>
+          <t>PDRN Pink Glutathione Capsule Foam Cleanser: espuma com PDRN e glutationa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2932,7 +2942,7 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>188.9</v>
+        <v>144.9</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
@@ -2941,15 +2951,15 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PDRN Pink Peptide Eye Cream</t>
+          <t>PDRN Pink Glutathione Capsule Foam Cleanser</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2958,7 +2968,7 @@
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-pink-peptide-eye-cream</t>
+          <t>https://medicube.us/products/pdrn-pink-glutathione-capsule-foam-cleanser</t>
         </is>
       </c>
       <c r="L44" s="2">
@@ -2973,12 +2983,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MB003328</t>
+          <t>MB003308</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PDRN Pink Peptide Toner: tônico com PDRN, niacinamida e peptídeos 250 ml</t>
+          <t>PDRN Pink Niacinamide Milky Toner: tônico leitoso com PDRN, ceramida e peptídeos</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2987,7 +2997,7 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>152.9</v>
+        <v>121.9</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
@@ -2996,26 +3006,22 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>PDRN Pink Peptide Toner</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Rose</t>
-        </is>
-      </c>
+          <t>PDRN Pink Niacinamide Milky Toner</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" s="4" t="n">
         <v>21</v>
       </c>
       <c r="I45" s="4" t="n"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-pink-peptide-toner-1?variant=42090422829104</t>
+          <t>https://medicube.us/products/pdrn-pink-niacinamide-milky-toner</t>
         </is>
       </c>
       <c r="L45" s="2">
@@ -3030,12 +3036,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MB003227</t>
+          <t>MB003327</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PDRN Pink Tension Up Mask: máscara tensora para queixo e contorno com PDRN</t>
+          <t>PDRN Pink One Day Serum: ampola de dose única com PDRN, colágeno e glutationa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3044,7 +3050,7 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>188.9</v>
+        <v>137.9</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
@@ -3053,15 +3059,15 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>PDRN Pink Tension Up Mask</t>
+          <t>PDRN Pink One Day Serum</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3070,7 +3076,7 @@
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-pink-tension-up-mask</t>
+          <t>https://medicube.us/products/pdrn-pink-one-day-serum</t>
         </is>
       </c>
       <c r="L46" s="2">
@@ -3085,12 +3091,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MB003311</t>
+          <t>MB003313</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PDRN Pink Vita Coating Sheet Mask: máscara em folha com PDRN e vitamina B12</t>
+          <t>PDRN Pink Peptide Eye Cream: creme para a área dos olhos com PDRN e retinol</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3099,7 +3105,7 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>174.9</v>
+        <v>188.9</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -3108,15 +3114,15 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>PDRN Pink Vita Coating Sheet Mask</t>
+          <t>PDRN Pink Peptide Eye Cream</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3125,7 +3131,7 @@
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-pink-vita-coating-sheet-mask</t>
+          <t>https://medicube.us/products/pdrn-pink-peptide-eye-cream</t>
         </is>
       </c>
       <c r="L47" s="2">
@@ -3140,12 +3146,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MB003266</t>
+          <t>MB003328</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Red Body Peeling Shot Cleanser: spray esfoliante corporal com 32% de ácidos 110 g</t>
+          <t>PDRN Pink Peptide Toner: tônico com PDRN, niacinamida e peptídeos 250 ml</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3154,7 +3160,7 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>174.9</v>
+        <v>152.9</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
@@ -3163,22 +3169,26 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Red Body Peeling Shot Cleanser</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>PDRN Pink Peptide Toner</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
       <c r="H48" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I48" s="4" t="n"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/red-body-peeling-shot-cleanser</t>
+          <t>https://medicube.us/products/pdrn-pink-peptide-toner-1?variant=42090422829104</t>
         </is>
       </c>
       <c r="L48" s="2">
@@ -3193,12 +3203,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MB003252</t>
+          <t>MB003227</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Red Body Wash: sabonete líquido corporal com ácido salicílico e niacinamida 400 ml</t>
+          <t>PDRN Pink Tension Up Mask: máscara tensora para queixo e contorno com PDRN</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3207,7 +3217,7 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>160.9</v>
+        <v>188.9</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
@@ -3216,28 +3226,24 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Red Body Wash</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>SINGLE</t>
-        </is>
-      </c>
+          <t>PDRN Pink Tension Up Mask</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/red-body-wash?variant=39919971205168</t>
+          <t>https://medicube.us/products/pdrn-pink-tension-up-mask</t>
         </is>
       </c>
       <c r="L49" s="2">
@@ -3252,12 +3258,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MB003258</t>
+          <t>MB003311</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Red Centellaca Mask: máscara calmante em 3 passos com centella e niacinamida</t>
+          <t>PDRN Pink Vita Coating Sheet Mask: máscara em folha com PDRN e vitamina B12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3266,7 +3272,7 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>35.9</v>
+        <v>174.9</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
@@ -3275,19 +3281,15 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Red Centellaca Mask</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>2 MASKS</t>
-        </is>
-      </c>
+          <t>PDRN Pink Vita Coating Sheet Mask</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" s="4" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -3296,7 +3298,7 @@
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/medicube-red-centellaca-mask-2ea?variant=40999720943664</t>
+          <t>https://medicube.us/products/pdrn-pink-vita-coating-sheet-mask</t>
         </is>
       </c>
       <c r="L50" s="2">
@@ -3311,12 +3313,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MB003265</t>
+          <t>MB003266</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Red Clear Capsule Body Lotion: loção corporal com cápsulas e ácidos 230 ml</t>
+          <t>Red Body Peeling Shot Cleanser: spray esfoliante corporal com 32% de ácidos 110 g</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3325,7 +3327,7 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>160.9</v>
+        <v>174.9</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
@@ -3334,16 +3336,14 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Red Clear Capsule Body Lotion</t>
+          <t>Red Body Peeling Shot Cleanser</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I51" s="4" t="n">
-        <v>23</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="I51" s="4" t="n"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/red-clear-capsule-body-lotion</t>
+          <t>https://medicube.us/products/red-body-peeling-shot-cleanser</t>
         </is>
       </c>
       <c r="L51" s="2">
@@ -3366,12 +3366,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MB003262</t>
+          <t>MB003252</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Red Foam Cleanser: espuma de limpeza com 0,45% de ácido salicílico 120 ml</t>
+          <t>Red Body Wash: sabonete líquido corporal com ácido salicílico e niacinamida 400 ml</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3380,7 +3380,7 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>144.9</v>
+        <v>160.9</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
@@ -3389,24 +3389,28 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Red Foam Cleanser</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
+          <t>Red Body Wash</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
       <c r="H52" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/red-foam-cleanser-120-ml</t>
+          <t>https://medicube.us/products/red-body-wash?variant=39919971205168</t>
         </is>
       </c>
       <c r="L52" s="2">
@@ -3421,12 +3425,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MB003247</t>
+          <t>MB003258</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Red Glow Body Essentials: rotina corporal com esfoliante, sabonete e loção</t>
+          <t>Red Centellaca Mask: máscara calmante em 3 passos com centella e niacinamida</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3435,7 +3439,7 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>176.9</v>
+        <v>35.9</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
@@ -3444,24 +3448,28 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Red Glow Body Essentials</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+          <t>Red Centellaca Mask</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2 MASKS</t>
+        </is>
+      </c>
       <c r="H53" s="4" t="n">
-        <v>24.3</v>
+        <v>5</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/red-glow-body-essentials</t>
+          <t>https://medicube.us/products/medicube-red-centellaca-mask-2ea?variant=40999720943664</t>
         </is>
       </c>
       <c r="L53" s="2">
@@ -3476,12 +3484,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MB003248</t>
+          <t>MB003265</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Red Line Full Set: rotina facial de 4 passos para pele oleosa</t>
+          <t>Red Clear Capsule Body Lotion: loção corporal com cápsulas e ácidos 230 ml</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3490,7 +3498,7 @@
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>802.9</v>
+        <v>160.9</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
@@ -3499,19 +3507,15 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Red Line Full Set</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Red Line Full Set</t>
-        </is>
-      </c>
+          <t>Red Clear Capsule Body Lotion</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" s="4" t="n">
-        <v>110</v>
+        <v>22</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>165</v>
+        <v>23</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -3520,7 +3524,7 @@
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/red-line-full-set?variant=41597301588016</t>
+          <t>https://medicube.us/products/red-clear-capsule-body-lotion</t>
         </is>
       </c>
       <c r="L54" s="2">
@@ -3535,12 +3539,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MB003246</t>
+          <t>MB003262</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Red Line Ultimate Face &amp; Body Care Set: rotina Red completa para rosto e corpo</t>
+          <t>Red Foam Cleanser: espuma de limpeza com 0,45% de ácido salicílico 120 ml</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3549,7 +3553,7 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>1255.9</v>
+        <v>144.9</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
@@ -3558,28 +3562,24 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Red Line Ultimate Face &amp; Body Care Set</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Red Line Ultimate Face &amp; Body Care Set</t>
-        </is>
-      </c>
+          <t>Red Foam Cleanser</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" s="4" t="n">
-        <v>172.2</v>
+        <v>20</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>246</v>
+        <v>22</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/red-line-ultimate-face-body-care-set?variant=41597303423024</t>
+          <t>https://medicube.us/products/red-foam-cleanser-120-ml</t>
         </is>
       </c>
       <c r="L55" s="2">
@@ -3594,12 +3594,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MB003264</t>
+          <t>MB003247</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Red Succinic Acid Panthenol Pads: discos de tônico para pele oleosa (70 discos)</t>
+          <t>Red Glow Body Essentials: rotina corporal com esfoliante, sabonete e loção</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3608,7 +3608,7 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>180.9</v>
+        <v>176.9</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -3617,28 +3617,24 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Red Succinic Acid Panthenol Pads</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>SINGLE</t>
-        </is>
-      </c>
+          <t>Red Glow Body Essentials</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" s="4" t="n">
-        <v>24.8</v>
+        <v>24.3</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/red-succinic-acid-panthenol-pads?variant=41268490960944</t>
+          <t>https://medicube.us/products/red-glow-body-essentials</t>
         </is>
       </c>
       <c r="L56" s="2">
@@ -3653,12 +3649,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MB003269</t>
+          <t>MB003248</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Retinol NMN Boosting Serum: sérum de retinol com NMN e peptídeos</t>
+          <t>Red Line Full Set: rotina facial de 4 passos para pele oleosa</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3667,7 +3663,7 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>174.9</v>
+        <v>802.9</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
@@ -3676,15 +3672,19 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Retinol NMN Boosting Serum</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
+          <t>Red Line Full Set</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Red Line Full Set</t>
+        </is>
+      </c>
       <c r="H57" s="4" t="n">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>26</v>
+        <v>165</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/retinol-nmn-boosting-serum</t>
+          <t>https://medicube.us/products/red-line-full-set?variant=41597301588016</t>
         </is>
       </c>
       <c r="L57" s="2">
@@ -3708,12 +3708,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MB003234</t>
+          <t>MB003246</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Rosemary PDRN Cooling Thickening Shampoo: shampoo refrescante de alecrim e PDRN</t>
+          <t>Red Line Ultimate Face &amp; Body Care Set: rotina Red completa para rosto e corpo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>188.9</v>
+        <v>1255.9</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
@@ -3731,24 +3731,28 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosemary PDRN Cooling Thickening Shampoo</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
+          <t>Red Line Ultimate Face &amp; Body Care Set</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Red Line Ultimate Face &amp; Body Care Set</t>
+        </is>
+      </c>
       <c r="H58" s="4" t="n">
-        <v>26</v>
+        <v>172.2</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>31</v>
+        <v>246</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/rosemary-pdrn-cooling-thickening-shampoo</t>
+          <t>https://medicube.us/products/red-line-ultimate-face-body-care-set?variant=41597303423024</t>
         </is>
       </c>
       <c r="L58" s="2">
@@ -3763,12 +3767,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MB003233</t>
+          <t>MB003264</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Rosemary PDRN Hair &amp; Scalp Conditioner: condicionador de alecrim com PDRN</t>
+          <t>Red Succinic Acid Panthenol Pads: discos de tônico para pele oleosa (70 discos)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3777,7 +3781,7 @@
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>188.9</v>
+        <v>180.9</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
@@ -3786,16 +3790,20 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosemary PDRN Hair &amp; Scalp Conditioner</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
+          <t>Red Succinic Acid Panthenol Pads</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
       <c r="H59" s="4" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="I59" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="I59" s="4" t="n">
-        <v>31</v>
-      </c>
       <c r="J59" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3803,7 +3811,7 @@
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/rosemary-pdrn-hair-scalp-conditioner</t>
+          <t>https://medicube.us/products/red-succinic-acid-panthenol-pads?variant=41268490960944</t>
         </is>
       </c>
       <c r="L59" s="2">
@@ -3818,12 +3826,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MB003232</t>
+          <t>MB003269</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Rosemary PDRN Scalp Serum: sérum para couro cabeludo com alecrim e PDRN</t>
+          <t>Retinol NMN Boosting Serum: sérum de retinol com NMN e peptídeos</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3832,7 +3840,7 @@
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>80.90000000000001</v>
+        <v>174.9</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
@@ -3841,12 +3849,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosemary PDRN Scalp Serum</t>
+          <t>Retinol NMN Boosting Serum</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" s="4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I60" s="4" t="n">
         <v>26</v>
@@ -3858,7 +3866,7 @@
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/rosemary-pdrn-scalp-serum</t>
+          <t>https://medicube.us/products/retinol-nmn-boosting-serum</t>
         </is>
       </c>
       <c r="L60" s="2">
@@ -3873,12 +3881,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MB003277</t>
+          <t>MB003234</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Super Cica Calming Mask: máscara em folha calmante com 7 tipos de centella</t>
+          <t>Rosemary PDRN Cooling Thickening Shampoo: shampoo refrescante de alecrim e PDRN</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3887,7 +3895,7 @@
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>42.9</v>
+        <v>188.9</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
@@ -3896,19 +3904,15 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Super Cica Calming Mask</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2 MASKS</t>
-        </is>
-      </c>
+          <t>Rosemary PDRN Cooling Thickening Shampoo</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" s="4" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3917,7 +3921,7 @@
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/super-cica-calming-mask?variant=40999721435184</t>
+          <t>https://medicube.us/products/rosemary-pdrn-cooling-thickening-shampoo</t>
         </is>
       </c>
       <c r="L61" s="2">
@@ -3932,12 +3936,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MB003274</t>
+          <t>MB003233</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Super Cica Daily Quick Masks: 30 máscaras calmantes de centella</t>
+          <t>Rosemary PDRN Hair &amp; Scalp Conditioner: condicionador de alecrim com PDRN</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3946,7 +3950,7 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>232.9</v>
+        <v>188.9</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
@@ -3955,19 +3959,15 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Super Cica Daily Quick Masks</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>SINGLE</t>
-        </is>
-      </c>
+          <t>Rosemary PDRN Hair &amp; Scalp Conditioner</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/super-cica-daily-quick-mask</t>
+          <t>https://medicube.us/products/rosemary-pdrn-hair-scalp-conditioner</t>
         </is>
       </c>
       <c r="L62" s="2">
@@ -3991,12 +3991,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MB003276</t>
+          <t>MB003232</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Super Cica Exfoliating Cleansing Balm: bálsamo de limpeza com centella 100 ml</t>
+          <t>Rosemary PDRN Scalp Serum: sérum para couro cabeludo com alecrim e PDRN</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>137.9</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Super Cica Exfoliating Cleansing Balm</t>
+          <t>Rosemary PDRN Scalp Serum</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -4022,7 +4022,7 @@
         <v>19</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/super-cica-exfoliating-cleansing-balm-vegan</t>
+          <t>https://medicube.us/products/rosemary-pdrn-scalp-serum</t>
         </is>
       </c>
       <c r="L63" s="2">
@@ -4046,12 +4046,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MB003275</t>
+          <t>MB003277</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Super Cica Toner: tônico calmante de centella sem álcool 210 ml</t>
+          <t>Super Cica Calming Mask: máscara em folha calmante com 7 tipos de centella</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4060,7 +4060,7 @@
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>115.9</v>
+        <v>42.9</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
@@ -4069,24 +4069,28 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Super Cica Toner</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+          <t>Super Cica Calming Mask</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2 MASKS</t>
+        </is>
+      </c>
       <c r="H64" s="4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/super-cica-water-in-toner</t>
+          <t>https://medicube.us/products/super-cica-calming-mask?variant=40999721435184</t>
         </is>
       </c>
       <c r="L64" s="2">
@@ -4101,12 +4105,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MB003293</t>
+          <t>MB003274</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TXA Niacinamide Capsule Cream: creme em cápsulas com ácido tranexâmico</t>
+          <t>Super Cica Daily Quick Masks: 30 máscaras calmantes de centella</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4115,7 +4119,7 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>188.9</v>
+        <v>232.9</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
@@ -4124,7 +4128,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>TXA Niacinamide Capsule Cream</t>
+          <t>Super Cica Daily Quick Masks</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4133,10 +4137,10 @@
         </is>
       </c>
       <c r="H65" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -4145,7 +4149,7 @@
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/txa-niacinamide-capsule-cream?variant=41980200288304</t>
+          <t>https://medicube.us/products/super-cica-daily-quick-mask</t>
         </is>
       </c>
       <c r="L65" s="2">
@@ -4160,12 +4164,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MB003294</t>
+          <t>MB003276</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TXA Niacinamide Serum: sérum com 5% de ácido tranexâmico e niacinamida</t>
+          <t>Super Cica Exfoliating Cleansing Balm: bálsamo de limpeza com centella 100 ml</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4174,7 +4178,7 @@
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>174.9</v>
+        <v>137.9</v>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
@@ -4183,15 +4187,15 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>TXA Niacinamide Serum</t>
+          <t>Super Cica Exfoliating Cleansing Balm</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -4200,7 +4204,7 @@
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/txa-niacinamide-serum</t>
+          <t>https://medicube.us/products/super-cica-exfoliating-cleansing-balm-vegan</t>
         </is>
       </c>
       <c r="L66" s="2">
@@ -4215,12 +4219,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MB003302</t>
+          <t>MB003275</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Triple Collagen Cream: creme de colágeno para hidratação e firmeza 50 ml</t>
+          <t>Super Cica Toner: tônico calmante de centella sem álcool 210 ml</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4229,7 +4233,7 @@
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>115.9</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
@@ -4238,28 +4242,24 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Triple Collagen Cream</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>SINGLE</t>
-        </is>
-      </c>
+          <t>Super Cica Toner</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/deep-erasing-cream?variant=40093603135536</t>
+          <t>https://medicube.us/products/super-cica-water-in-toner</t>
         </is>
       </c>
       <c r="L67" s="2">
@@ -4274,12 +4274,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MB003301</t>
+          <t>MB003293</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Triple Collagen Serum: sérum com três tipos de colágeno e niacinamida 55 ml</t>
+          <t>TXA Niacinamide Capsule Cream: creme em cápsulas com ácido tranexâmico</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>254.9</v>
+        <v>188.9</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
@@ -4297,15 +4297,19 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Triple Collagen Serum</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
+          <t>TXA Niacinamide Capsule Cream</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
       <c r="H68" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -4314,7 +4318,7 @@
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/triple-collagen-serum</t>
+          <t>https://medicube.us/products/txa-niacinamide-capsule-cream?variant=41980200288304</t>
         </is>
       </c>
       <c r="L68" s="2">
@@ -4329,12 +4333,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MB003256</t>
+          <t>MB003294</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Triple Collagen Toner: tônico hidratante com 3 tipos de colágeno 140 ml</t>
+          <t>TXA Niacinamide Serum: sérum com 5% de ácido tranexâmico e niacinamida</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4343,7 +4347,7 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>225.9</v>
+        <v>174.9</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
@@ -4352,14 +4356,16 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Triple Collagen Toner</t>
+          <t>TXA Niacinamide Serum</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="I69" s="4" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>26</v>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4367,7 +4373,7 @@
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/glass-glow-essence-2-0</t>
+          <t>https://medicube.us/products/txa-niacinamide-serum</t>
         </is>
       </c>
       <c r="L69" s="2">
@@ -4382,12 +4388,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MB003320</t>
+          <t>MB003302</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Zero Exosome Shot: sérum com microespículas para poros 30 ml</t>
+          <t>Triple Collagen Cream: creme de colágeno para hidratação e firmeza 50 ml</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4396,7 +4402,7 @@
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>145.9</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
@@ -4405,19 +4411,19 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Zero Exosome Shot</t>
+          <t>Triple Collagen Cream</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>MILD(2000)</t>
+          <t>SINGLE</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -4426,7 +4432,7 @@
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/exosome-shot?variant=41200136519728</t>
+          <t>https://medicube.us/products/deep-erasing-cream?variant=40093603135536</t>
         </is>
       </c>
       <c r="L70" s="2">
@@ -4441,12 +4447,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MB003286</t>
+          <t>MB003301</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Zero Foam Cleanser: espuma de limpeza para poros e oleosidade</t>
+          <t>Triple Collagen Serum: sérum com três tipos de colágeno e niacinamida 55 ml</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4455,7 +4461,7 @@
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>110.9</v>
+        <v>254.9</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
@@ -4464,15 +4470,15 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Zero Foam Cleanser</t>
+          <t>Triple Collagen Serum</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -4481,7 +4487,7 @@
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/zero-foam-cleanser</t>
+          <t>https://medicube.us/products/triple-collagen-serum</t>
         </is>
       </c>
       <c r="L71" s="2">
@@ -4496,12 +4502,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MB003283</t>
+          <t>MB003256</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Zero Line Full Set: discos, sérum e creme Zero Pore para poros</t>
+          <t>Triple Collagen Toner: tônico hidratante com 3 tipos de colágeno 140 ml</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4510,7 +4516,7 @@
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>480.9</v>
+        <v>225.9</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
@@ -4519,16 +4525,14 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Zero Line Full Set</t>
+          <t>Triple Collagen Toner</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="I72" s="4" t="n">
-        <v>110</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I72" s="4" t="n"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4536,7 +4540,7 @@
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/new-zero-line-full-set</t>
+          <t>https://medicube.us/products/glass-glow-essence-2-0</t>
         </is>
       </c>
       <c r="L72" s="2">
@@ -4551,12 +4555,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MB003321</t>
+          <t>MB003320</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Zero Pore Blackhead Deep Cleansing Oil: óleo de limpeza para cravos e maquiagem</t>
+          <t>Zero Exosome Shot: sérum com microespículas para poros 30 ml</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4565,7 +4569,7 @@
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>152.9</v>
+        <v>145.9</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
@@ -4574,19 +4578,19 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Zero Pore Blackhead Deep Cleansing Oil</t>
+          <t>Zero Exosome Shot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SINGLE</t>
+          <t>MILD(2000)</t>
         </is>
       </c>
       <c r="H73" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -4595,7 +4599,7 @@
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/zero-pore-blackhead-deep-cleansing-oil?variant=41865193947184</t>
+          <t>https://medicube.us/products/exosome-shot?variant=41200136519728</t>
         </is>
       </c>
       <c r="L73" s="2">
@@ -4610,12 +4614,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MB003291</t>
+          <t>MB003286</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Zero Pore Capsule Cleansing Foam: espuma de limpeza com microcápsulas para poros</t>
+          <t>Zero Foam Cleanser: espuma de limpeza para poros e oleosidade</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4633,7 +4637,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Zero Pore Capsule Cleansing Foam</t>
+          <t>Zero Foam Cleanser</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -4650,7 +4654,7 @@
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/zero-pore-clear-blue-capsule-facial-deep-cleanser</t>
+          <t>https://medicube.us/products/zero-foam-cleanser</t>
         </is>
       </c>
       <c r="L74" s="2">
@@ -4665,12 +4669,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MB003289</t>
+          <t>MB003283</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Zero Pore Cooling Mask: máscara em folha refrescante para poros</t>
+          <t>Zero Line Full Set: discos, sérum e creme Zero Pore para poros</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4679,7 +4683,7 @@
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>18.9</v>
+        <v>480.9</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
@@ -4688,19 +4692,15 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Zero Pore Cooling Mask</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>2 MASKS</t>
-        </is>
-      </c>
+          <t>Zero Line Full Set</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" s="4" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>12</v>
+        <v>110</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="K75" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/zero-pore-cooling-mask?variant=40999560871984</t>
+          <t>https://medicube.us/products/new-zero-line-full-set</t>
         </is>
       </c>
       <c r="L75" s="2">
@@ -4724,12 +4724,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MB003287</t>
+          <t>MB003321</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Zero Pore One-day Cream: hidratante para poros e pele oleosa 50 ml</t>
+          <t>Zero Pore Blackhead Deep Cleansing Oil: óleo de limpeza para cravos e maquiagem</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4738,7 +4738,7 @@
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>157.9</v>
+        <v>152.9</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
@@ -4747,15 +4747,19 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Zero Pore One-day Cream</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr"/>
+          <t>Zero Pore Blackhead Deep Cleansing Oil</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
       <c r="H76" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -4764,7 +4768,7 @@
       </c>
       <c r="K76" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/zero-pore-one-day-cream</t>
+          <t>https://medicube.us/products/zero-pore-blackhead-deep-cleansing-oil?variant=41865193947184</t>
         </is>
       </c>
       <c r="L76" s="2">
@@ -4779,12 +4783,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MB003288</t>
+          <t>MB003291</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Zero Pore One-day Peptide Serum: sérum para poros com 10 peptídeos e ácidos 30 ml</t>
+          <t>Zero Pore Capsule Cleansing Foam: espuma de limpeza com microcápsulas para poros</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4793,7 +4797,7 @@
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>145.9</v>
+        <v>110.9</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
@@ -4802,15 +4806,15 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Zero Pore One-day Peptide Serum</t>
+          <t>Zero Pore Capsule Cleansing Foam</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -4819,7 +4823,7 @@
       </c>
       <c r="K77" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/zero-pore-one-day-serum</t>
+          <t>https://medicube.us/products/zero-pore-clear-blue-capsule-facial-deep-cleanser</t>
         </is>
       </c>
       <c r="L77" s="2">
@@ -4834,12 +4838,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MB003290</t>
+          <t>MB003289</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Zero Pore Toner: tônico esfoliante e hidratante com AHA, BHA, PHA e niacinamida</t>
+          <t>Zero Pore Cooling Mask: máscara em folha refrescante para poros</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4848,7 +4852,7 @@
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>152.9</v>
+        <v>18.9</v>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
@@ -4857,14 +4861,20 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Zero Pore Toner</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
+          <t>Zero Pore Cooling Mask</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2 MASKS</t>
+        </is>
+      </c>
       <c r="H78" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="I78" s="4" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="I78" s="4" t="n">
+        <v>12</v>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4872,7 +4882,7 @@
       </c>
       <c r="K78" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/zero-pore-toner</t>
+          <t>https://medicube.us/products/zero-pore-cooling-mask?variant=40999560871984</t>
         </is>
       </c>
       <c r="L78" s="2">
@@ -4887,21 +4897,21 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MB003299</t>
+          <t>MB003287</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Overnight Wrapping Mask: máscara noturna de cúrcuma e ácido kójico</t>
+          <t>Zero Pore One-day Cream: hidratante para poros e pele oleosa 50 ml</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>139.9</v>
+        <v>157.9</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
@@ -4910,18 +4920,16 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Overnight Wrapping Mask</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>SINGLE</t>
-        </is>
-      </c>
+          <t>Zero Pore One-day Cream</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I79" s="4" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="I79" s="4" t="n">
+        <v>34</v>
+      </c>
       <c r="J79" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4929,7 +4937,7 @@
       </c>
       <c r="K79" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/kojic-acid-tumeric-overnight-wrapping-mask?variant=41896883159088</t>
+          <t>https://medicube.us/products/zero-pore-one-day-cream</t>
         </is>
       </c>
       <c r="L79" s="2">
@@ -4944,12 +4952,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MB003323</t>
+          <t>MB003288</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Affordable Glass Glow 7-Day Set: rotina de 5 passos com exossomos e colágeno</t>
+          <t>Zero Pore One-day Peptide Serum: sérum para poros com 10 peptídeos e ácidos 30 ml</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4958,28 +4966,24 @@
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>561.9</v>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>145.9</v>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Affordable Glass Glow 7-Day Skincare Set</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Collagen Jelly Cream</t>
-        </is>
-      </c>
+          <t>Zero Pore One-day Peptide Serum</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" s="4" t="n">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>155</v>
+        <v>26</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -4988,7 +4992,7 @@
       </c>
       <c r="K80" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/affordable-glass-glow-7-day-skincare-set?variant=41592205738032</t>
+          <t>https://medicube.us/products/zero-pore-one-day-serum</t>
         </is>
       </c>
       <c r="L80" s="2">
@@ -5003,12 +5007,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MB003304</t>
+          <t>MB003290</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Collagen Glow Bubble Serum: sérum em mousse com 11 tipos de colágeno 100 ml</t>
+          <t>Zero Pore Toner: tônico esfoliante e hidratante com AHA, BHA, PHA e niacinamida</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5017,25 +5021,23 @@
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>174.9</v>
-      </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>152.9</v>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>[US ONLY] Collagen Glow Bubble Serum</t>
+          <t>Zero Pore Toner</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I81" s="4" t="n">
-        <v>26</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I81" s="4" t="n"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -5043,7 +5045,7 @@
       </c>
       <c r="K81" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/collagen-glow-bubble-serum</t>
+          <t>https://medicube.us/products/zero-pore-toner</t>
         </is>
       </c>
       <c r="L81" s="2">
@@ -5058,51 +5060,47 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MB003245</t>
+          <t>MB003279</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Conjunto AGE-R Spotless Radiance</t>
+          <t>Adesivo Deep Vita C</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>2179.9</v>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>109</v>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AGE-R Spotless Radiance Set</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Pink</t>
-        </is>
-      </c>
+          <t>Deep Vita C Patch</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" s="4" t="n">
-        <v>299</v>
+        <v>19</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>529</v>
+        <v>21</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K82" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/age-r-spotless-radiance-set?variant=41769865838640</t>
+          <t>https://medicube.us/products/deep-vita-c-patch</t>
         </is>
       </c>
       <c r="L82" s="2">
@@ -5117,39 +5115,41 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MB003255</t>
+          <t>MB003299</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Deep Glow Set: tônico, sérum e creme de colágeno em 3 passos</t>
+          <t>Kojic Acid Turmeric Overnight Wrapping Mask: máscara noturna de cúrcuma e ácido kójico</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>509.9</v>
-      </c>
-      <c r="E83" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>139.9</v>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Deep Glow Set</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr"/>
+          <t>Kojic Acid Turmeric Overnight Wrapping Mask</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
       <c r="H83" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="I83" s="4" t="n">
-        <v>109</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="I83" s="4" t="n"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="K83" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/deep-glow-set-1</t>
+          <t>https://medicube.us/products/kojic-acid-tumeric-overnight-wrapping-mask?variant=41896883159088</t>
         </is>
       </c>
       <c r="L83" s="2">
@@ -5172,12 +5172,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MB003282</t>
+          <t>MB003245</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deep Vita C Capsule Cream: creme em cápsulas de vitamina C e niacinamida 55 g</t>
+          <t>Conjunto AGE-R Spotless Radiance</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5186,7 +5186,7 @@
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>169.9</v>
+        <v>2179.9</v>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
@@ -5195,28 +5195,28 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Deep Vita C Capsule Cream</t>
+          <t>AGE-R Spotless Radiance Set</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SINGLE</t>
+          <t>Pink</t>
         </is>
       </c>
       <c r="H84" s="4" t="n">
-        <v>26</v>
+        <v>299</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>34</v>
+        <v>529</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K84" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/deep-vita-c-capsule-cream?variant=41431644799024</t>
+          <t>https://medicube.us/products/age-r-spotless-radiance-set?variant=41769865838640</t>
         </is>
       </c>
       <c r="L84" s="2">
@@ -5231,12 +5231,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MB003242</t>
+          <t>MB003255</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Hypochlorous Acid Rice Peel Shot: peeling facial com ácido hipocloroso e arroz</t>
+          <t>Deep Glow Set: tônico, sérum e creme de colágeno em 3 passos</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>189.9</v>
+        <v>509.9</v>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
@@ -5254,14 +5254,16 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Hypochlorous Acid Rice Peel Shot</t>
+          <t>Deep Glow Set</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="I85" s="4" t="n"/>
+        <v>70</v>
+      </c>
+      <c r="I85" s="4" t="n">
+        <v>109</v>
+      </c>
       <c r="J85" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -5269,7 +5271,7 @@
       </c>
       <c r="K85" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/hypochlorous-acid-rice-peel-shot</t>
+          <t>https://medicube.us/products/deep-glow-set-1</t>
         </is>
       </c>
       <c r="L85" s="2">
@@ -5284,12 +5286,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MB003236</t>
+          <t>MB003282</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Peel Shot: sérum esfoliante de enxágue com ácido kójico</t>
+          <t>Deep Vita C Capsule Cream: creme em cápsulas de vitamina C e niacinamida 55 g</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5298,7 +5300,7 @@
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>175.9</v>
+        <v>169.9</v>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
@@ -5307,15 +5309,19 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Peel Shot</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr"/>
+          <t>Deep Vita C Capsule Cream</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
       <c r="H86" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -5324,7 +5330,7 @@
       </c>
       <c r="K86" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/kojic-acid-turmeric-peel-shot</t>
+          <t>https://medicube.us/products/deep-vita-c-capsule-cream?variant=41431644799024</t>
         </is>
       </c>
       <c r="L86" s="2">
@@ -5339,12 +5345,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MB003296</t>
+          <t>MB003242</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Toner: tônico com ácido kójico e cúrcuma para rosto e corpo</t>
+          <t>Hypochlorous Acid Rice Peel Shot: peeling facial com ácido hipocloroso e arroz</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5353,7 +5359,7 @@
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>153.9</v>
+        <v>189.9</v>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
@@ -5362,12 +5368,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kojic Acid Turmeric Toner</t>
+          <t>Hypochlorous Acid Rice Peel Shot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" s="4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I87" s="4" t="n"/>
       <c r="J87" t="inlineStr">
@@ -5377,7 +5383,7 @@
       </c>
       <c r="K87" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/kojic-acid-turmeric-toner</t>
+          <t>https://medicube.us/products/hypochlorous-acid-rice-peel-shot</t>
         </is>
       </c>
       <c r="L87" s="2">
@@ -5392,12 +5398,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MB003330</t>
+          <t>MB003236</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PDRN Pink Collagen Capsule Cream: creme em cápsulas com PDRN e colágeno 55 g</t>
+          <t>Kojic Acid Turmeric Peel Shot: sérum esfoliante de enxágue com ácido kójico</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5406,7 +5412,7 @@
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>169.9</v>
+        <v>175.9</v>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
@@ -5415,20 +5421,16 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>PDRN Pink Collagen Capsule Cream</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>SINGLE</t>
-        </is>
-      </c>
+          <t>Kojic Acid Turmeric Peel Shot</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I88" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="I88" s="4" t="n">
-        <v>34</v>
-      </c>
       <c r="J88" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -5436,7 +5438,7 @@
       </c>
       <c r="K88" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-pink-collagen-capsule-cream?variant=41902192230448</t>
+          <t>https://medicube.us/products/kojic-acid-turmeric-peel-shot</t>
         </is>
       </c>
       <c r="L88" s="2">
@@ -5451,12 +5453,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MB003325</t>
+          <t>MB003296</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PDRN Pink Collagen Glow Jelly Mist Serum: sérum em bruma com PDRN e colágeno</t>
+          <t>Kojic Acid Turmeric Toner: tônico com ácido kójico e cúrcuma para rosto e corpo</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5465,7 +5467,7 @@
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>151.9</v>
+        <v>153.9</v>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
@@ -5474,20 +5476,14 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>PDRN Pink Collagen Glow Jelly Mist Serum</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>100ml</t>
-        </is>
-      </c>
+          <t>Kojic Acid Turmeric Toner</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I89" s="4" t="n">
-        <v>28</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I89" s="4" t="n"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -5495,7 +5491,7 @@
       </c>
       <c r="K89" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-jelly-mist?variant=43624682881072</t>
+          <t>https://medicube.us/products/kojic-acid-turmeric-toner</t>
         </is>
       </c>
       <c r="L89" s="2">
@@ -5510,12 +5506,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MB003239</t>
+          <t>MB003330</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PDRN Pink Collagen Glow Jelly Serum: sérum em gel com PDRN, colágeno e niacinamida</t>
+          <t>PDRN Pink Collagen Capsule Cream: creme em cápsulas com PDRN e colágeno 55 g</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5524,7 +5520,7 @@
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>174.9</v>
+        <v>169.9</v>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
@@ -5533,19 +5529,19 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>PDRN Pink Collagen Glow Jelly Mist Serum</t>
+          <t>PDRN Pink Collagen Capsule Cream</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>SINGLE</t>
         </is>
       </c>
       <c r="H90" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -5554,7 +5550,7 @@
       </c>
       <c r="K90" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-jelly-mist?variant=43624682881072</t>
+          <t>https://medicube.us/products/pdrn-pink-collagen-capsule-cream?variant=41902192230448</t>
         </is>
       </c>
       <c r="L90" s="2">
@@ -5569,12 +5565,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MB003316</t>
+          <t>MB003325</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PDRN Pink Glow Full Set: tônico, sérum e creme com PDRN</t>
+          <t>PDRN Pink Collagen Glow Jelly Mist Serum: sérum em bruma com PDRN e colágeno</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5583,7 +5579,7 @@
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>655.9</v>
+        <v>151.9</v>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
@@ -5592,28 +5588,28 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>PDRN Pink Glow Full Set</t>
+          <t>PDRN Pink Collagen Glow Jelly Mist Serum</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rose PDRN (Vegan)</t>
+          <t>100ml</t>
         </is>
       </c>
       <c r="H91" s="4" t="n">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>95.98</v>
+        <v>28</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K91" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-exosome-set?variant=41729848508464</t>
+          <t>https://medicube.us/products/pdrn-jelly-mist?variant=43624682881072</t>
         </is>
       </c>
       <c r="L91" s="2">
@@ -5628,12 +5624,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MB003326</t>
+          <t>MB003239</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PDRN Pink Peptide Cream: hidratante leve com PDRN e ácido hialurônico 50 ml</t>
+          <t>PDRN Pink Collagen Glow Jelly Serum: sérum em gel com PDRN, colágeno e niacinamida</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5642,7 +5638,7 @@
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>188.9</v>
+        <v>174.9</v>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
@@ -5651,12 +5647,16 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>PDRN Pink Peptide Eye Cream</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr"/>
+          <t>PDRN Pink Collagen Glow Jelly Mist Serum</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
       <c r="H92" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I92" s="4" t="n">
         <v>28</v>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="K92" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-pink-peptide-eye-cream</t>
+          <t>https://medicube.us/products/pdrn-jelly-mist?variant=43624682881072</t>
         </is>
       </c>
       <c r="L92" s="2">
@@ -5683,12 +5683,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MB003312</t>
+          <t>MB003326</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PDRN Pink Peptide Serum: sérum de PDRN com peptídeos e niacinamida 30 ml</t>
+          <t>PDRN Pink Peptide Cream: hidratante leve com PDRN e ácido hialurônico 50 ml</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5697,7 +5697,7 @@
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>133.9</v>
+        <v>188.9</v>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
@@ -5706,19 +5706,15 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ultra Light PDRN Pink Peptide Serum</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Light PDRN (30ml)</t>
-        </is>
-      </c>
+          <t>PDRN Pink Peptide Eye Cream</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" s="4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -5727,7 +5723,7 @@
       </c>
       <c r="K93" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/ultra-light-pdrn-pink-peptide-serum?variant=43308557795376</t>
+          <t>https://medicube.us/products/pdrn-pink-peptide-eye-cream</t>
         </is>
       </c>
       <c r="L93" s="2">
@@ -5742,12 +5738,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MB003284</t>
+          <t>MB003312</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Pore Care Duo: sérum Zero Pore One-day 30 ml + creme Zero Pore One-day 50 ml</t>
+          <t>PDRN Pink Peptide Serum: sérum de PDRN com peptídeos e niacinamida 30 ml</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5756,7 +5752,7 @@
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>328.9</v>
+        <v>133.9</v>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
@@ -5765,15 +5761,19 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pore Care Duo</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr"/>
+          <t>Ultra Light PDRN Pink Peptide Serum</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Light PDRN (30ml)</t>
+        </is>
+      </c>
       <c r="H94" s="4" t="n">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="K94" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/new-pore-care-duo-set</t>
+          <t>https://medicube.us/products/ultra-light-pdrn-pink-peptide-serum?variant=43308557795376</t>
         </is>
       </c>
       <c r="L94" s="2">
@@ -5797,12 +5797,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MB003260</t>
+          <t>MB003284</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Red Serum: sérum calmante com melaleuca para pele oleosa 30 ml</t>
+          <t>Pore Care Duo: sérum Zero Pore One-day 30 ml + creme Zero Pore One-day 50 ml</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5811,7 +5811,7 @@
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>144.9</v>
+        <v>328.9</v>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
@@ -5820,15 +5820,15 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Red Serum</t>
+          <t>Pore Care Duo</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" s="4" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="I95" s="4" t="n">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="K95" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/red-serum</t>
+          <t>https://medicube.us/products/new-pore-care-duo-set</t>
         </is>
       </c>
       <c r="L95" s="2">
@@ -5852,12 +5852,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MB003261</t>
+          <t>MB003260</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Red Toner: tônico calmante com extratos de plantas para pele oleosa 100 ml</t>
+          <t>Red Serum: sérum calmante com melaleuca para pele oleosa 30 ml</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>115.9</v>
+        <v>144.9</v>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
@@ -5875,15 +5875,15 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Red Toner</t>
+          <t>Red Serum</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="K96" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/red-toner</t>
+          <t>https://medicube.us/products/red-serum</t>
         </is>
       </c>
       <c r="L96" s="2">
@@ -5907,12 +5907,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MB003315</t>
+          <t>MB003261</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Salmon PDRN Pink Collagen Jelly Gel Mask: máscara de gel com PDRN que muda de cor</t>
+          <t>Red Toner: tônico calmante com extratos de plantas para pele oleosa 100 ml</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>175.9</v>
+        <v>115.9</v>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
@@ -5930,19 +5930,15 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Salmon PDRN Pink Collagen Jelly Gel Mask</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>1EA</t>
-        </is>
-      </c>
+          <t>Red Toner</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" s="4" t="n">
-        <v>5.99</v>
+        <v>16</v>
       </c>
       <c r="I97" s="4" t="n">
-        <v>6.99</v>
+        <v>21</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -5951,7 +5947,7 @@
       </c>
       <c r="K97" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-pink-collagen-gel-mask?variant=41631127633968</t>
+          <t>https://medicube.us/products/red-toner</t>
         </is>
       </c>
       <c r="L97" s="2">
@@ -5966,12 +5962,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MB003285</t>
+          <t>MB003315</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Zero Pore Blackhead Mud Mask: máscara de argila para cravos que seca em 3 minutos 100 g</t>
+          <t>Salmon PDRN Pink Collagen Jelly Gel Mask: máscara de gel com PDRN que muda de cor</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5980,7 +5976,7 @@
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>110.9</v>
+        <v>175.9</v>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
@@ -5989,19 +5985,19 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Zero Pore Blackhead Deep Cleansing Oil</t>
+          <t>Salmon PDRN Pink Collagen Jelly Gel Mask</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Deep Pore (+Zero Mud Mask)</t>
+          <t>1EA</t>
         </is>
       </c>
       <c r="H98" s="4" t="n">
-        <v>37</v>
+        <v>5.99</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>49</v>
+        <v>6.99</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -6010,7 +6006,7 @@
       </c>
       <c r="K98" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/zero-pore-blackhead-deep-cleansing-oil?variant=41865193979952</t>
+          <t>https://medicube.us/products/pdrn-pink-collagen-gel-mask?variant=41631127633968</t>
         </is>
       </c>
       <c r="L98" s="2">
@@ -6025,12 +6021,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MB003322</t>
+          <t>MB003285</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Zero Pore Pads: discos esfoliantes para poros com AHA e BHA (70 discos)</t>
+          <t>Zero Pore Blackhead Mud Mask: máscara de argila para cravos que seca em 3 minutos 100 g</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6039,7 +6035,7 @@
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>152.9</v>
+        <v>110.9</v>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
@@ -6048,7 +6044,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Zero Pore Pads</t>
+          <t>Zero Pore Blackhead Mud Mask</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6057,11 +6053,11 @@
         </is>
       </c>
       <c r="H99" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I99" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="I99" s="4" t="n">
-        <v>31</v>
-      </c>
       <c r="J99" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -6069,7 +6065,7 @@
       </c>
       <c r="K99" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/zero-pore-pad-1?variant=40542710825008</t>
+          <t>https://medicube.us/products/zero-pore-blackhead-mud-mask?variant=41200159883312</t>
         </is>
       </c>
       <c r="L99" s="2">
@@ -6084,12 +6080,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MB003251</t>
+          <t>MB003322</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Máscara Deep Vita C</t>
+          <t>Zero Pore Pads: discos esfoliantes para poros com AHA e BHA (70 discos)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6098,24 +6094,28 @@
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>137.9</v>
-      </c>
-      <c r="E100" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>152.9</v>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Deep Vita C Daily Quick Masks</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr"/>
+          <t>Zero Pore Pads</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
       <c r="H100" s="4" t="n">
         <v>24</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="K100" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/deep-vita-c-daily-quick-masks</t>
+          <t>https://medicube.us/products/zero-pore-pad-1?variant=40542710825008</t>
         </is>
       </c>
       <c r="L100" s="2">
@@ -6139,38 +6139,42 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MB003272</t>
+          <t>MB003271</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Sérum em gel booster</t>
+          <t>Creme Vita K</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>101.9</v>
-      </c>
-      <c r="E101" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>73</v>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>PDRN Booster Gel</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr"/>
+          <t>Deep Vita C Capsule Cream</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
       <c r="H101" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I101" s="4" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -6179,7 +6183,7 @@
       </c>
       <c r="K101" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/pdrn-booster-gel</t>
+          <t>https://medicube.us/products/deep-vita-c-capsule-cream?variant=41431644799024</t>
         </is>
       </c>
       <c r="L101" s="2">
@@ -6194,12 +6198,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MB003279</t>
+          <t>MB003987</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Adesivo Deep Vita C</t>
+          <t>Kit PDRN Colágeno Rosa Glow</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6208,33 +6212,37 @@
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="E102" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>656.9</v>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Deep Vita C Patch</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr"/>
+          <t>PDRN Pink Glow Full Set</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Rose PDRN (Vegan)</t>
+        </is>
+      </c>
       <c r="H102" s="4" t="n">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>21</v>
+        <v>95.98</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K102" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/deep-vita-c-patch</t>
+          <t>https://medicube.us/products/pdrn-exosome-set?variant=41729848508464</t>
         </is>
       </c>
       <c r="L102" s="2">
@@ -6249,12 +6257,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MB003271</t>
+          <t>MB003253</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Creme Vita K</t>
+          <t>Sérum Iluminador com Glutationa AGE-R</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6263,29 +6271,25 @@
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="E103" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>145.9</v>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Deep Vita C Capsule Cream</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>SINGLE</t>
-        </is>
-      </c>
+          <t>AGE-R Glutathione Glow Serum</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I103" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="I103" s="4" t="n">
-        <v>34</v>
-      </c>
       <c r="J103" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -6293,7 +6297,7 @@
       </c>
       <c r="K103" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/deep-vita-c-capsule-cream?variant=41431644799024</t>
+          <t>https://medicube.us/products/age-r-glutathione-glow-serum</t>
         </is>
       </c>
       <c r="L103" s="2">
@@ -6308,21 +6312,21 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MB003987</t>
+          <t>MB003251</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Kit PDRN Colágeno Rosa Glow</t>
+          <t>Máscara Deep Vita C</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>656.9</v>
+        <v>137.9</v>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
@@ -6331,19 +6335,15 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ultimate PDRN 2X Glow Set</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Pink</t>
-        </is>
-      </c>
+          <t>Deep Vita C Daily Quick Masks</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" s="4" t="n">
-        <v>279</v>
+        <v>24</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>351</v>
+        <v>35</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="K104" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/ultimate-pdrn-2x-glow-set?variant=43604705345584</t>
+          <t>https://medicube.us/products/deep-vita-c-daily-quick-masks</t>
         </is>
       </c>
       <c r="L104" s="2">
@@ -6367,21 +6367,21 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MB003259</t>
+          <t>MB003272</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Red Cream</t>
+          <t>Sérum em gel booster</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>114</v>
+        <v>101.9</v>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
@@ -6390,15 +6390,15 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>3H Daily Relief Cream</t>
+          <t>PDRN Booster Gel</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="I105" s="4" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="K105" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/3h-daily-relief-cream</t>
+          <t>https://medicube.us/products/pdrn-booster-gel</t>
         </is>
       </c>
       <c r="L105" s="2">
@@ -6422,12 +6422,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MB003253</t>
+          <t>MB003270</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Sérum Iluminador com Glutationa AGE-R</t>
+          <t>Lenços de Limpeza</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6436,7 +6436,7 @@
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>145.9</v>
+        <v>18.9</v>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
@@ -6445,15 +6445,15 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>AGE-R Glutathione Glow Serum</t>
+          <t>Cleansing Wipes</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" s="4" t="n">
-        <v>24</v>
+        <v>2.5</v>
       </c>
       <c r="I106" s="4" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="K106" s="5" t="inlineStr">
         <is>
-          <t>https://medicube.us/products/age-r-glutathione-glow-serum</t>
+          <t>https://medicube.us/products/age-r-cleansing-wipes</t>
         </is>
       </c>
       <c r="L106" s="2">
@@ -6477,50 +6477,76 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MB003273</t>
+          <t>MB003259</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Creme em Cápsulas AGE-R Glutathione Glow</t>
+          <t>Red Cream</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>174.9</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H107" s="4" t="n"/>
-      <c r="I107" s="4" t="n"/>
-      <c r="L107" s="2" t="n"/>
-      <c r="M107" s="6" t="n"/>
+        <v>114</v>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>3H Daily Relief Cream</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="I107" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="inlineStr">
+        <is>
+          <t>https://medicube.us/products/3h-daily-relief-cream</t>
+        </is>
+      </c>
+      <c r="L107" s="2">
+        <f>ROUND(H107*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M107" s="6">
+        <f>IF(OR(D107="",L107=""),"",D107/L107-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MB003249</t>
+          <t>MB003273</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Discos de Tônico Calmante com Exossomos e Centella Asiática</t>
+          <t>Creme em Cápsulas AGE-R Glutathione Glow</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>247.9</v>
+        <v>174.9</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -6535,12 +6561,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MB003333</t>
+          <t>MB003249</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Kit Completo de Cuidados Rosa e Dourado</t>
+          <t>Discos de Tônico Calmante com Exossomos e Centella Asiática</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6549,7 +6575,7 @@
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>2252.9</v>
+        <v>247.9</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -6564,12 +6590,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MB003270</t>
+          <t>MB003333</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Lenços de Limpeza</t>
+          <t>Kit Completo de Cuidados Rosa e Dourado</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6578,7 +6604,7 @@
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>18.9</v>
+        <v>2252.9</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -6755,10 +6781,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId106"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId106"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId107"/>
   </tableParts>
 </worksheet>
 </file>
@@ -15549,7 +15576,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site oficial: https://medicube.us · loja "MEDICUBE US" · moeda USD · lido em 30/10/2026 06:05 UTC</t>
+          <t>Site oficial: https://medicube.us · loja "MEDICUBE US" · moeda USD · lido em 30/10/2026 06:07 UTC</t>
         </is>
       </c>
     </row>
